--- a/Pteropod_summary_MeCa.xlsx
+++ b/Pteropod_summary_MeCa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clairesheppard/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EB8EF0-CBA7-7E41-8731-DD5AD98C50D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD36991-2FA6-7C48-B28B-E0E5A8DC7B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="1480" windowWidth="27020" windowHeight="16440" firstSheet="3" activeTab="9" xr2:uid="{8C9521DA-CBBE-964C-8613-3A9834640F7F}"/>
+    <workbookView xWindow="60" yWindow="1480" windowWidth="28700" windowHeight="16440" activeTab="1" xr2:uid="{8C9521DA-CBBE-964C-8613-3A9834640F7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="193">
   <si>
     <t>12-4</t>
   </si>
@@ -615,6 +615,15 @@
   </si>
   <si>
     <t>salinity at thermocline</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number </t>
   </si>
 </sst>
 </file>
@@ -664,7 +673,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,12 +689,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,7 +718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +748,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -744,16 +759,18 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1112,6 +1129,9 @@
       <c r="M1" t="s">
         <v>31</v>
       </c>
+      <c r="N1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -1151,6 +1171,9 @@
       <c r="M2">
         <v>37.824234563318797</v>
       </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1190,6 +1213,9 @@
       <c r="M3">
         <v>86.44551374776627</v>
       </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1229,6 +1255,9 @@
       <c r="M4">
         <v>192.53405332023902</v>
       </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1268,6 +1297,9 @@
       <c r="M5">
         <v>47.584717245536574</v>
       </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1307,6 +1339,9 @@
       <c r="M6">
         <v>11.240396518217807</v>
       </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1346,6 +1381,9 @@
       <c r="M7">
         <v>314.18405452370484</v>
       </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1385,6 +1423,9 @@
       <c r="M8">
         <v>10.179775574037372</v>
       </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1424,6 +1465,9 @@
       <c r="M9">
         <v>91.912710611649771</v>
       </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1463,6 +1507,9 @@
       <c r="M10">
         <v>13.389546649879703</v>
       </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1502,6 +1549,9 @@
       <c r="M11">
         <v>30.743648026756269</v>
       </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -1541,6 +1591,9 @@
       <c r="M12">
         <v>170.20697097150486</v>
       </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1580,6 +1633,9 @@
       <c r="M13">
         <v>24.357999230689543</v>
       </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1619,6 +1675,9 @@
       <c r="M14">
         <v>192.74606876714873</v>
       </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1658,6 +1717,9 @@
       <c r="M15">
         <v>122.79761862196219</v>
       </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1696,6 +1758,9 @@
       <c r="M16">
         <v>513.90317393468467</v>
       </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
       <c r="P16" t="s">
         <v>58</v>
       </c>
@@ -1770,6 +1835,9 @@
       <c r="M17">
         <v>627.11718748768214</v>
       </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
       <c r="P17" t="s">
         <v>58</v>
       </c>
@@ -1845,6 +1913,9 @@
       <c r="M18">
         <v>548.66957616592072</v>
       </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
       <c r="P18" t="s">
         <v>58</v>
       </c>
@@ -1921,6 +1992,9 @@
       <c r="M19">
         <v>219.93697957266215</v>
       </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
       <c r="P19" t="s">
         <v>58</v>
       </c>
@@ -1997,6 +2071,9 @@
       <c r="M20">
         <v>156.34316228209411</v>
       </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
       <c r="P20" t="s">
         <v>58</v>
       </c>
@@ -2073,6 +2150,9 @@
       <c r="M21">
         <v>141.92032139848197</v>
       </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
       <c r="P21" t="s">
         <v>58</v>
       </c>
@@ -2149,6 +2229,9 @@
       <c r="M22">
         <v>72.380084089451174</v>
       </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
       <c r="P22" t="s">
         <v>58</v>
       </c>
@@ -2225,6 +2308,9 @@
       <c r="M23">
         <v>53.637733087144142</v>
       </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
       <c r="P23" t="s">
         <v>58</v>
       </c>
@@ -2301,6 +2387,9 @@
       <c r="M24">
         <v>59.876917988874879</v>
       </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
       <c r="P24" t="s">
         <v>58</v>
       </c>
@@ -2377,6 +2466,9 @@
       <c r="M25">
         <v>45.282253824305165</v>
       </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
       <c r="P25" t="s">
         <v>58</v>
       </c>
@@ -2453,6 +2545,9 @@
       <c r="M26">
         <v>62.512748584023385</v>
       </c>
+      <c r="N26">
+        <v>4</v>
+      </c>
       <c r="P26" t="s">
         <v>58</v>
       </c>
@@ -2529,6 +2624,9 @@
       <c r="M27">
         <v>46.069786166823988</v>
       </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
       <c r="P27" t="s">
         <v>58</v>
       </c>
@@ -2605,6 +2703,9 @@
       <c r="M28">
         <v>42.292238756116532</v>
       </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -2734,7 +2835,7 @@
         <v>262.70779801455848</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2758,7 +2859,7 @@
         <v>280.87195861435953</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2782,7 +2883,7 @@
         <v>19.586506653739349</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2806,7 +2907,7 @@
         <v>139.64951763061828</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -2844,8 +2945,11 @@
       <c r="M36">
         <v>201.55003627239822</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -2883,8 +2987,11 @@
       <c r="M37">
         <v>174.50818201290463</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -2922,8 +3029,11 @@
       <c r="M38">
         <v>26.353884770157411</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -2961,8 +3071,11 @@
       <c r="M39">
         <v>111.76200703682701</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -3000,8 +3113,11 @@
       <c r="M40">
         <v>121.65943856354582</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -3039,8 +3155,11 @@
       <c r="M41">
         <v>156.07035135394165</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -3078,8 +3197,11 @@
       <c r="M42">
         <v>35.592166881550789</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -3117,8 +3239,11 @@
       <c r="M43">
         <v>20.539170496042239</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -3156,8 +3281,11 @@
       <c r="M44">
         <v>143.08753497233951</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -3195,8 +3323,11 @@
       <c r="M45">
         <v>93.972518031999115</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -3234,8 +3365,11 @@
       <c r="M46">
         <v>70.280899721910259</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -3273,8 +3407,11 @@
       <c r="M47">
         <v>588.26064575105306</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>33</v>
       </c>
@@ -3312,8 +3449,11 @@
       <c r="M48">
         <v>183.7360895710282</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -3351,8 +3491,11 @@
       <c r="M49">
         <v>106.88888921316737</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>33</v>
       </c>
@@ -3390,8 +3533,11 @@
       <c r="M50">
         <v>66.97128896449189</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>33</v>
       </c>
@@ -3429,8 +3575,11 @@
       <c r="M51">
         <v>103.39171008586746</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>33</v>
       </c>
@@ -3468,58 +3617,61 @@
       <c r="M52">
         <v>1135.9102008285563</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="G64" s="1"/>
@@ -3527,8 +3679,8 @@
     <row r="65" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="3:7" x14ac:dyDescent="0.2">
@@ -3634,8 +3786,8 @@
     <row r="86" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="3:7" x14ac:dyDescent="0.2">
@@ -3895,1943 +4047,2289 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3F7547-7462-974B-B6A7-2E1E312B7BC2}">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" customWidth="1"/>
-    <col min="14" max="14" width="43.33203125" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.1640625" customWidth="1"/>
+    <col min="15" max="15" width="43.33203125" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>32</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="P1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>128</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>127</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="18">
+        <v>44475</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.72368374488545484</v>
+      </c>
+      <c r="H2">
+        <v>5.1239409469326826</v>
+      </c>
+      <c r="I2">
+        <v>24.593890076209743</v>
+      </c>
+      <c r="J2">
+        <v>51.382073750158312</v>
+      </c>
+      <c r="K2">
+        <v>0.30552330966207991</v>
+      </c>
+      <c r="L2">
+        <v>18.000350203003009</v>
+      </c>
+      <c r="M2">
+        <v>18.908057017564776</v>
+      </c>
+      <c r="N2">
+        <v>30.743648026756269</v>
+      </c>
+      <c r="O2" s="18">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="18">
+        <v>44491</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.88656105008731589</v>
+      </c>
+      <c r="H3">
+        <v>21.274117579071415</v>
+      </c>
+      <c r="I3">
+        <v>34.826061251676549</v>
+      </c>
+      <c r="J3">
+        <v>52.508533848807922</v>
+      </c>
+      <c r="K3">
+        <v>0.21065496754629021</v>
+      </c>
+      <c r="L3">
+        <v>24.521995784066746</v>
+      </c>
+      <c r="M3">
+        <v>8.7833807384011191</v>
+      </c>
+      <c r="N3">
+        <v>10.179775574037372</v>
+      </c>
+      <c r="O3" s="18">
+        <v>44491</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="17">
+        <v>44495</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0.81336733202131484</v>
+      </c>
+      <c r="H4">
+        <v>21.186105772811882</v>
+      </c>
+      <c r="I4">
+        <v>15.801180336692479</v>
+      </c>
+      <c r="J4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" t="s">
+        <v>121</v>
+      </c>
+      <c r="M4" t="s">
+        <v>121</v>
+      </c>
+      <c r="N4" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="17">
+        <v>44496</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0.87057806018547423</v>
+      </c>
+      <c r="H5">
+        <v>16.354827881837799</v>
+      </c>
+      <c r="I5">
+        <v>19.586506653739349</v>
+      </c>
+      <c r="J5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" t="s">
+        <v>121</v>
+      </c>
+      <c r="L5" t="s">
+        <v>121</v>
+      </c>
+      <c r="M5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N5" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="17">
+        <v>44497</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0.82943994592263348</v>
+      </c>
+      <c r="H6">
+        <v>9.1531551300475531</v>
+      </c>
+      <c r="I6">
+        <v>32.173873045758981</v>
+      </c>
+      <c r="J6">
+        <v>103.26174930766932</v>
+      </c>
+      <c r="K6">
+        <v>0.22714613772822062</v>
+      </c>
+      <c r="L6">
+        <v>9.9785579303476677</v>
+      </c>
+      <c r="M6">
+        <v>9.8085980896599594</v>
+      </c>
+      <c r="N6">
+        <v>20.539170496042239</v>
+      </c>
+      <c r="O6" s="17">
+        <v>44497</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="17">
+        <v>44526</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.80580079156721263</v>
+      </c>
+      <c r="H7">
+        <v>10.874727826601507</v>
+      </c>
+      <c r="I7">
+        <v>38.925032797494872</v>
+      </c>
+      <c r="J7">
+        <v>37.09827270225238</v>
+      </c>
+      <c r="K7">
+        <v>0.27591285814979949</v>
+      </c>
+      <c r="L7">
+        <v>18.322747332495339</v>
+      </c>
+      <c r="M7">
+        <v>44.210126018127731</v>
+      </c>
+      <c r="N7">
+        <v>86.44551374776627</v>
+      </c>
+      <c r="O7" s="17">
+        <v>44526</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>130</v>
+      </c>
+      <c r="R7">
+        <f>(4*1)/1</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="18">
+        <v>44527</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0.84973561934755426</v>
+      </c>
+      <c r="H8">
+        <v>10.471283552733373</v>
+      </c>
+      <c r="I8">
+        <v>45.514254168321237</v>
+      </c>
+      <c r="J8">
+        <v>37.130635802367529</v>
+      </c>
+      <c r="K8">
+        <v>0.24353026866796124</v>
+      </c>
+      <c r="L8">
+        <v>17.220231271854207</v>
+      </c>
+      <c r="M8">
+        <v>9.3829871741436826</v>
+      </c>
+      <c r="N8">
+        <v>11.240396518217807</v>
+      </c>
+      <c r="O8" s="18">
+        <v>44527</v>
+      </c>
+      <c r="P8">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R8">
+        <f>(1*5)/5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="17">
+        <v>44528</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0.9162235079877068</v>
+      </c>
+      <c r="H9">
+        <v>24.545744470135475</v>
+      </c>
+      <c r="I9">
+        <v>61.937779563104371</v>
+      </c>
+      <c r="J9">
+        <v>173.89847383049559</v>
+      </c>
+      <c r="K9">
+        <v>1.0827120164312798</v>
+      </c>
+      <c r="L9">
+        <v>19.315274981928059</v>
+      </c>
+      <c r="M9">
+        <v>136.73734233042214</v>
+      </c>
+      <c r="N9">
+        <v>156.07035135394165</v>
+      </c>
+      <c r="O9" s="17">
+        <v>44528</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>133</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="18">
+        <v>44529</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1.2222271505973339</v>
+      </c>
+      <c r="H10">
+        <v>11.038185180700172</v>
+      </c>
+      <c r="I10">
+        <v>48.536706315537195</v>
+      </c>
+      <c r="J10">
+        <v>96.735988018993396</v>
+      </c>
+      <c r="K10">
+        <v>0.29030406206297854</v>
+      </c>
+      <c r="L10">
+        <v>10.660638353397356</v>
+      </c>
+      <c r="M10">
+        <v>32.022127097341219</v>
+      </c>
+      <c r="N10">
+        <v>24.357999230689543</v>
+      </c>
+      <c r="O10" s="18">
+        <v>44529</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>137</v>
+      </c>
+      <c r="R10">
+        <f>((3)+(2*2))/P10</f>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="17">
+        <v>44530</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0.86536802145215086</v>
+      </c>
+      <c r="H11">
+        <v>20.795897804959665</v>
+      </c>
+      <c r="I11">
+        <v>61.336338232269597</v>
+      </c>
+      <c r="J11">
+        <v>77.776681989483095</v>
+      </c>
+      <c r="K11">
+        <v>0.32887870460706831</v>
+      </c>
+      <c r="L11">
+        <v>21.817958441671976</v>
+      </c>
+      <c r="M11">
+        <v>63.694457909015462</v>
+      </c>
+      <c r="N11">
+        <v>121.65943856354582</v>
+      </c>
+      <c r="O11" s="17">
+        <v>44530</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>140</v>
+      </c>
+      <c r="R11">
+        <f>(1*10)/P11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="17">
+        <v>44531</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>0.77073714592290399</v>
+      </c>
+      <c r="H12">
+        <v>18.418874611647716</v>
+      </c>
+      <c r="I12">
+        <v>43.484155321149728</v>
+      </c>
+      <c r="J12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" s="17"/>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>139</v>
+      </c>
+      <c r="R12">
+        <f>((3*1)+(1*2))/P12</f>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="17">
+        <v>44532</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>0.8763828636338783</v>
+      </c>
+      <c r="H13">
+        <v>12.79266909986408</v>
+      </c>
+      <c r="I13">
+        <v>44.383724815034029</v>
+      </c>
+      <c r="J13">
+        <v>48.063124119531857</v>
+      </c>
+      <c r="K13">
+        <v>0.25528721534446464</v>
+      </c>
+      <c r="L13">
+        <v>27.042002636147195</v>
+      </c>
+      <c r="M13">
+        <v>16.096262547244134</v>
+      </c>
+      <c r="N13">
+        <v>35.592166881550789</v>
+      </c>
+      <c r="O13" s="17">
+        <v>44532</v>
+      </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>138</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="17">
+        <v>44534</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>0.96133627112180253</v>
+      </c>
+      <c r="H14">
+        <v>18.017795753185347</v>
+      </c>
+      <c r="I14">
+        <v>92.879600778978642</v>
+      </c>
+      <c r="J14">
+        <v>43.978994852749935</v>
+      </c>
+      <c r="K14">
+        <v>0.43728866100165364</v>
+      </c>
+      <c r="L14">
+        <v>19.323630536464208</v>
+      </c>
+      <c r="M14">
+        <v>59.864140596331971</v>
+      </c>
+      <c r="N14">
+        <v>1135.9102008285563</v>
+      </c>
+      <c r="O14" s="17">
+        <v>44534</v>
+      </c>
+      <c r="P14">
+        <v>28</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>148</v>
+      </c>
+      <c r="R14">
+        <f>((2*5)+(1*3)+(3*20))/P14</f>
+        <v>2.6071428571428572</v>
+      </c>
+      <c r="S14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="18">
+        <v>44535</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0.87932182745812371</v>
+      </c>
+      <c r="H15">
+        <v>15.618258396167157</v>
+      </c>
+      <c r="I15">
+        <v>64.022076659602547</v>
+      </c>
+      <c r="J15">
+        <v>37.024975322509512</v>
+      </c>
+      <c r="K15">
+        <v>0.2696689918686821</v>
+      </c>
+      <c r="L15">
+        <v>17.070944140937719</v>
+      </c>
+      <c r="M15">
+        <v>41.704638382757388</v>
+      </c>
+      <c r="N15">
+        <v>47.584717245536574</v>
+      </c>
+      <c r="O15" s="18">
+        <v>44535</v>
+      </c>
+      <c r="P15">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="Q15" t="s">
+        <v>132</v>
+      </c>
+      <c r="R15">
+        <f>((5*4)+(4*2)+(1*2)+2)/P15</f>
+        <v>3.5555555555555554</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="17">
+        <v>44539</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>0.91621224397381784</v>
+      </c>
+      <c r="H16">
+        <v>25.058629677997317</v>
+      </c>
+      <c r="I16">
+        <v>68.788490017426341</v>
+      </c>
+      <c r="J16">
+        <v>58.706022354485512</v>
+      </c>
+      <c r="K16">
+        <v>0.48295423573591645</v>
+      </c>
+      <c r="L16">
+        <v>17.003137623904195</v>
+      </c>
+      <c r="M16">
+        <v>108.40397354403991</v>
+      </c>
+      <c r="N16">
+        <v>103.39171008586746</v>
+      </c>
+      <c r="O16" s="17">
+        <v>44539</v>
+      </c>
+      <c r="P16">
+        <v>19</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>147</v>
+      </c>
+      <c r="R16">
+        <f>((1*8)+(2*6)+(4*2)+(5)+(3*2))/19</f>
+        <v>2.0526315789473686</v>
+      </c>
+      <c r="S16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="17">
+        <v>44538</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>0.95693048723895513</v>
+      </c>
+      <c r="H17">
+        <v>17.080523833436768</v>
+      </c>
+      <c r="I17">
+        <v>73.156940447001503</v>
+      </c>
+      <c r="J17">
+        <v>29.573130556837636</v>
+      </c>
+      <c r="K17">
+        <v>0.3797858517718064</v>
+      </c>
+      <c r="L17">
+        <v>16.380057403292973</v>
+      </c>
+      <c r="M17">
+        <v>38.341861069609458</v>
+      </c>
+      <c r="N17">
+        <v>66.97128896449189</v>
+      </c>
+      <c r="O17" s="17">
+        <v>44538</v>
+      </c>
+      <c r="P17">
+        <v>13</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="17">
+        <v>44539</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D2">
+      <c r="F18">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="G18">
         <v>0.80933442637431929</v>
       </c>
-      <c r="F2">
+      <c r="H18">
         <v>8.5803896552124019</v>
       </c>
-      <c r="G2">
+      <c r="I18">
         <v>349.33938408922165</v>
       </c>
-      <c r="H2">
+      <c r="J18">
         <v>27.134223195237617</v>
       </c>
-      <c r="I2">
+      <c r="K18">
         <v>0.96107202444760242</v>
       </c>
-      <c r="J2">
+      <c r="L18">
         <v>24.006529318345894</v>
       </c>
-      <c r="K2">
+      <c r="M18">
         <v>23.481281407349556</v>
       </c>
-      <c r="L2">
+      <c r="N18">
         <v>37.824234563318797</v>
       </c>
-      <c r="M2">
+      <c r="O18" s="17">
+        <v>44539</v>
+      </c>
+      <c r="P18">
         <v>4</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q18" t="s">
         <v>129</v>
       </c>
-      <c r="O2">
+      <c r="R18">
         <f>(1*4)/4</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="18">
+        <v>44543</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>0.80580079156721263</v>
-      </c>
-      <c r="F3">
-        <v>10.874727826601507</v>
-      </c>
-      <c r="G3">
-        <v>38.925032797494872</v>
-      </c>
-      <c r="H3">
-        <v>37.09827270225238</v>
-      </c>
-      <c r="I3">
-        <v>0.27591285814979949</v>
-      </c>
-      <c r="J3">
-        <v>18.322747332495339</v>
-      </c>
-      <c r="K3">
-        <v>44.210126018127731</v>
-      </c>
-      <c r="L3">
-        <v>86.44551374776627</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-      <c r="N3" t="s">
-        <v>130</v>
-      </c>
-      <c r="O3">
-        <f>(4*1)/1</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+      <c r="G19">
         <v>0.78902058669226527</v>
       </c>
-      <c r="F4">
+      <c r="H19">
         <v>21.85266026837348</v>
       </c>
-      <c r="G4">
+      <c r="I19">
         <v>486.48239756691532</v>
       </c>
-      <c r="H4">
+      <c r="J19">
         <v>42.10435597115773</v>
       </c>
-      <c r="I4">
+      <c r="K19">
         <v>1.0102772948184773</v>
       </c>
-      <c r="J4">
+      <c r="L19">
         <v>28.939842343182082</v>
       </c>
-      <c r="K4">
+      <c r="M19">
         <v>199.02388947971676</v>
       </c>
-      <c r="L4">
+      <c r="N19">
         <v>192.53405332023902</v>
       </c>
-      <c r="M4">
+      <c r="O19" s="18">
+        <v>44543</v>
+      </c>
+      <c r="P19">
         <v>7</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q19" t="s">
         <v>131</v>
       </c>
-      <c r="O4">
+      <c r="R19">
         <f>((3*3)+(2*1)+(5)+(4*2))/7</f>
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0.87932182745812371</v>
-      </c>
-      <c r="F5">
-        <v>15.618258396167157</v>
-      </c>
-      <c r="G5">
-        <v>64.022076659602547</v>
-      </c>
-      <c r="H5">
-        <v>37.024975322509512</v>
-      </c>
-      <c r="I5">
-        <v>0.2696689918686821</v>
-      </c>
-      <c r="J5">
-        <v>17.070944140937719</v>
-      </c>
-      <c r="K5">
-        <v>41.704638382757388</v>
-      </c>
-      <c r="L5">
-        <v>47.584717245536574</v>
-      </c>
-      <c r="M5">
-        <v>9</v>
-      </c>
-      <c r="N5" t="s">
-        <v>132</v>
-      </c>
-      <c r="O5">
-        <f>((5*4)+(4*2)+(1*2)+2)/M5</f>
-        <v>3.5555555555555554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0.84973561934755426</v>
-      </c>
-      <c r="F6">
-        <v>10.471283552733373</v>
-      </c>
-      <c r="G6">
-        <v>45.514254168321237</v>
-      </c>
-      <c r="H6">
-        <v>37.130635802367529</v>
-      </c>
-      <c r="I6">
-        <v>0.24353026866796124</v>
-      </c>
-      <c r="J6">
-        <v>17.220231271854207</v>
-      </c>
-      <c r="K6">
-        <v>9.3829871741436826</v>
-      </c>
-      <c r="L6">
-        <v>11.240396518217807</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6" t="s">
-        <v>133</v>
-      </c>
-      <c r="O6">
-        <f>(1*5)/5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0.86501924334796854</v>
-      </c>
-      <c r="F7">
-        <v>35.748985570739016</v>
-      </c>
-      <c r="G7">
-        <v>395.46611857587158</v>
-      </c>
-      <c r="H7">
-        <v>57.563021246709916</v>
-      </c>
-      <c r="I7">
-        <v>1.2318368301159066</v>
-      </c>
-      <c r="J7">
-        <v>25.513000106482657</v>
-      </c>
-      <c r="K7">
-        <v>272.54910509264789</v>
-      </c>
-      <c r="L7">
-        <v>314.18405452370484</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0.88656105008731589</v>
-      </c>
-      <c r="F8">
-        <v>21.274117579071415</v>
-      </c>
-      <c r="G8">
-        <v>34.826061251676549</v>
-      </c>
-      <c r="H8">
-        <v>52.508533848807922</v>
-      </c>
-      <c r="I8">
-        <v>0.21065496754629021</v>
-      </c>
-      <c r="J8">
-        <v>24.521995784066746</v>
-      </c>
-      <c r="K8">
-        <v>8.7833807384011191</v>
-      </c>
-      <c r="L8">
-        <v>10.179775574037372</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0.9279084140152204</v>
-      </c>
-      <c r="F9">
-        <v>48.102592972145246</v>
-      </c>
-      <c r="G9">
-        <v>219.37686437793496</v>
-      </c>
-      <c r="H9">
-        <v>57.652621836731157</v>
-      </c>
-      <c r="I9">
-        <v>0.5398836848281815</v>
-      </c>
-      <c r="J9">
-        <v>9.9502613620541265</v>
-      </c>
-      <c r="K9">
-        <v>112.65266362091219</v>
-      </c>
-      <c r="L9">
-        <v>91.912710611649771</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-      <c r="N9" t="s">
-        <v>134</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>0.80702183651452364</v>
-      </c>
-      <c r="F10">
-        <v>10.455680618415109</v>
-      </c>
-      <c r="G10">
-        <v>178.87378354518839</v>
-      </c>
-      <c r="H10">
-        <v>40.299038984451677</v>
-      </c>
-      <c r="I10">
-        <v>0.27233494334137037</v>
-      </c>
-      <c r="J10">
-        <v>7.8353679661454105</v>
-      </c>
-      <c r="K10">
-        <v>9.4100335939093522</v>
-      </c>
-      <c r="L10">
-        <v>13.389546649879703</v>
-      </c>
-      <c r="M10">
-        <v>7</v>
-      </c>
-      <c r="N10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O10">
-        <f>((5*2)+(4*2)+(3*3))/M10</f>
-        <v>3.8571428571428572</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0.72368374488545484</v>
-      </c>
-      <c r="F11">
-        <v>5.1239409469326826</v>
-      </c>
-      <c r="G11">
-        <v>24.593890076209743</v>
-      </c>
-      <c r="H11">
-        <v>51.382073750158312</v>
-      </c>
-      <c r="I11">
-        <v>0.30552330966207991</v>
-      </c>
-      <c r="J11">
-        <v>18.000350203003009</v>
-      </c>
-      <c r="K11">
-        <v>18.908057017564776</v>
-      </c>
-      <c r="L11">
-        <v>30.743648026756269</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0.96161313509105339</v>
-      </c>
-      <c r="F12">
-        <v>23.964656258597035</v>
-      </c>
-      <c r="G12">
-        <v>469.12717995209761</v>
-      </c>
-      <c r="H12">
-        <v>41.903309867642157</v>
-      </c>
-      <c r="I12">
-        <v>0.63607330014090313</v>
-      </c>
-      <c r="J12">
-        <v>9.1039868773002333</v>
-      </c>
-      <c r="K12">
-        <v>125.28663377666911</v>
-      </c>
-      <c r="L12">
-        <v>170.20697097150486</v>
-      </c>
-      <c r="M12">
-        <v>8</v>
-      </c>
-      <c r="N12" t="s">
-        <v>136</v>
-      </c>
-      <c r="O12">
-        <f>((3*5)+(1*1)+(4*2))/M12</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1.2222271505973339</v>
-      </c>
-      <c r="F13">
-        <v>11.038185180700172</v>
-      </c>
-      <c r="G13">
-        <v>48.536706315537195</v>
-      </c>
-      <c r="H13">
-        <v>96.735988018993396</v>
-      </c>
-      <c r="I13">
-        <v>0.29030406206297854</v>
-      </c>
-      <c r="J13">
-        <v>10.660638353397356</v>
-      </c>
-      <c r="K13">
-        <v>32.022127097341219</v>
-      </c>
-      <c r="L13">
-        <v>24.357999230689543</v>
-      </c>
-      <c r="M13">
-        <v>3</v>
-      </c>
-      <c r="N13" t="s">
-        <v>137</v>
-      </c>
-      <c r="O13">
-        <f>((3)+(2*2))/M13</f>
-        <v>2.3333333333333335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1.035875758861204</v>
-      </c>
-      <c r="F14">
-        <v>6.7968407717507775</v>
-      </c>
-      <c r="G14">
-        <v>133.26966325321399</v>
-      </c>
-      <c r="H14">
-        <v>87.803690847940175</v>
-      </c>
-      <c r="I14">
-        <v>0.67431164589372905</v>
-      </c>
-      <c r="J14">
-        <v>8.6857484126838305</v>
-      </c>
-      <c r="K14">
-        <v>135.8285002973293</v>
-      </c>
-      <c r="L14">
-        <v>192.74606876714873</v>
-      </c>
-      <c r="M14">
-        <v>4</v>
-      </c>
-      <c r="N14" t="s">
-        <v>129</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>0.92188121713274906</v>
-      </c>
-      <c r="F15">
-        <v>42.027593789363983</v>
-      </c>
-      <c r="G15">
-        <v>186.15008319723404</v>
-      </c>
-      <c r="H15">
-        <v>39.633014680025624</v>
-      </c>
-      <c r="I15">
-        <v>0.32814841295460101</v>
-      </c>
-      <c r="J15">
-        <v>11.031716815464861</v>
-      </c>
-      <c r="K15">
-        <v>105.33504986099311</v>
-      </c>
-      <c r="L15">
-        <v>122.79761862196219</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>0.95926114347927749</v>
-      </c>
-      <c r="F16">
-        <v>12.066556365700901</v>
-      </c>
-      <c r="G16">
-        <v>161.92274315291311</v>
-      </c>
-      <c r="H16">
-        <v>52.3487620801763</v>
-      </c>
-      <c r="I16">
-        <v>0.64003041011396244</v>
-      </c>
-      <c r="J16">
-        <v>16.514215278927544</v>
-      </c>
-      <c r="K16">
-        <v>25.154315378283385</v>
-      </c>
-      <c r="L16">
-        <v>42.292238756116532</v>
-      </c>
-      <c r="M16">
-        <v>6</v>
-      </c>
-      <c r="N16" t="s">
-        <v>142</v>
-      </c>
-      <c r="O16">
-        <f>((1*4)+(2*2))/M16</f>
-        <v>1.3333333333333333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>0.72199635922676897</v>
-      </c>
-      <c r="F17">
-        <v>27.097383191755213</v>
-      </c>
-      <c r="G17">
-        <v>277.34523327873609</v>
-      </c>
-      <c r="H17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" t="s">
-        <v>121</v>
-      </c>
-      <c r="J17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>121</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>2</v>
-      </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>0.81336733202131484</v>
-      </c>
-      <c r="F18">
-        <v>21.186105772811882</v>
-      </c>
-      <c r="G18">
-        <v>15.801180336692479</v>
-      </c>
-      <c r="H18" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" t="s">
-        <v>121</v>
-      </c>
-      <c r="J18" t="s">
-        <v>121</v>
-      </c>
-      <c r="K18" t="s">
-        <v>121</v>
-      </c>
-      <c r="L18" t="s">
-        <v>121</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>0.77073714592290399</v>
-      </c>
-      <c r="F19">
-        <v>18.418874611647716</v>
-      </c>
-      <c r="G19">
-        <v>43.484155321149728</v>
-      </c>
-      <c r="H19" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" t="s">
-        <v>121</v>
-      </c>
-      <c r="J19" t="s">
-        <v>121</v>
-      </c>
-      <c r="K19" t="s">
-        <v>121</v>
-      </c>
-      <c r="L19" t="s">
-        <v>121</v>
-      </c>
-      <c r="M19">
-        <v>3</v>
-      </c>
-      <c r="N19" t="s">
-        <v>139</v>
-      </c>
-      <c r="O19">
-        <f>((3*1)+(1*2))/M19</f>
-        <v>1.6666666666666667</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20">
+        <v>82</v>
+      </c>
+      <c r="C20" s="17">
+        <v>44544</v>
+      </c>
+      <c r="D20" s="3">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="E20">
-        <v>0.71925333016162252</v>
-      </c>
-      <c r="F20">
-        <v>31.627582864321159</v>
-      </c>
       <c r="G20">
-        <v>262.70779801455848</v>
-      </c>
-      <c r="H20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" t="s">
-        <v>121</v>
-      </c>
-      <c r="J20" t="s">
-        <v>121</v>
-      </c>
-      <c r="K20" t="s">
-        <v>121</v>
-      </c>
-      <c r="L20" t="s">
-        <v>121</v>
+        <v>0.93919756584407754</v>
+      </c>
+      <c r="H20">
+        <v>22.187098222622993</v>
+      </c>
+      <c r="I20">
+        <v>232.81284658384095</v>
+      </c>
+      <c r="J20">
+        <v>40.850015817504392</v>
+      </c>
+      <c r="K20">
+        <v>0.66836608660612418</v>
+      </c>
+      <c r="L20">
+        <v>25.3112561871514</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>70.140545151448066</v>
       </c>
       <c r="N20">
-        <v>5</v>
-      </c>
-      <c r="O20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>70.280899721910259</v>
+      </c>
+      <c r="O20" s="17">
+        <v>44544</v>
+      </c>
+      <c r="P20">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>143</v>
+      </c>
+      <c r="R20">
+        <f>((1*4)+(2*6))/10</f>
+        <v>1.6</v>
+      </c>
+      <c r="S20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21">
+        <v>85</v>
+      </c>
+      <c r="C21" s="17">
+        <v>44546</v>
+      </c>
+      <c r="D21" s="3">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="E21">
-        <v>0.85938488401942481</v>
-      </c>
-      <c r="F21">
-        <v>27.654924218398499</v>
-      </c>
       <c r="G21">
-        <v>280.87195861435953</v>
-      </c>
-      <c r="H21" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J21" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" t="s">
-        <v>121</v>
+        <v>0.90619233447163783</v>
+      </c>
+      <c r="H21">
+        <v>60.278407692382387</v>
+      </c>
+      <c r="I21">
+        <v>289.48893995925721</v>
+      </c>
+      <c r="J21">
+        <v>92.398845717450115</v>
+      </c>
+      <c r="K21">
+        <v>0.71666422027219223</v>
+      </c>
+      <c r="L21">
+        <v>18.511438084366794</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>68.829706823466779</v>
       </c>
       <c r="N21">
-        <v>3</v>
-      </c>
-      <c r="O21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <v>106.88888921316737</v>
+      </c>
+      <c r="O21" s="17">
+        <v>44546</v>
+      </c>
+      <c r="P21">
+        <v>14</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>144</v>
+      </c>
+      <c r="R21">
+        <f>((5*1)+(1*3)+(2*10))/P21</f>
+        <v>2</v>
+      </c>
+      <c r="S21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22">
+        <v>84</v>
+      </c>
+      <c r="C22" s="17">
+        <v>44545</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="E22">
-        <v>0.87057806018547423</v>
-      </c>
-      <c r="F22">
-        <v>16.354827881837799</v>
-      </c>
       <c r="G22">
-        <v>19.586506653739349</v>
-      </c>
-      <c r="H22" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" t="s">
-        <v>121</v>
-      </c>
-      <c r="K22" t="s">
-        <v>121</v>
-      </c>
-      <c r="L22" t="s">
-        <v>121</v>
+        <v>0.90431285410188522</v>
+      </c>
+      <c r="H22">
+        <v>27.000145839646486</v>
+      </c>
+      <c r="I22">
+        <v>184.55978829978042</v>
+      </c>
+      <c r="J22">
+        <v>35.304299846378434</v>
+      </c>
+      <c r="K22">
+        <v>0.62191082466464265</v>
+      </c>
+      <c r="L22">
+        <v>16.860920307063587</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>46.7958548160343</v>
       </c>
       <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>183.7360895710282</v>
+      </c>
+      <c r="O22" s="17">
+        <v>44545</v>
+      </c>
+      <c r="P22">
+        <v>14</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>145</v>
+      </c>
+      <c r="R22">
+        <f>((2*7)+(1*6)+(3*1))/14</f>
+        <v>1.6428571428571428</v>
+      </c>
+      <c r="S22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23">
+        <v>83</v>
+      </c>
+      <c r="C23" s="17">
+        <v>44549</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="E23">
-        <v>0.76182168425168695</v>
-      </c>
-      <c r="F23">
-        <v>49.075023070080348</v>
-      </c>
       <c r="G23">
-        <v>139.64951763061828</v>
-      </c>
-      <c r="H23" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" t="s">
-        <v>121</v>
-      </c>
-      <c r="J23" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" t="s">
-        <v>121</v>
-      </c>
-      <c r="L23" t="s">
-        <v>121</v>
+        <v>0.83825396406271191</v>
+      </c>
+      <c r="H23">
+        <v>79.565372082083343</v>
+      </c>
+      <c r="I23">
+        <v>310.58409849330383</v>
+      </c>
+      <c r="J23">
+        <v>51.97966949576584</v>
+      </c>
+      <c r="K23">
+        <v>1.187180700809771</v>
+      </c>
+      <c r="L23">
+        <v>51.782563142503037</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>386.60748366088694</v>
       </c>
       <c r="N23">
-        <v>5</v>
-      </c>
-      <c r="O23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>588.26064575105306</v>
+      </c>
+      <c r="O23" s="17">
+        <v>44549</v>
+      </c>
+      <c r="P23">
+        <v>22</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>149</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>0.89073325978086304</v>
+        <v>19</v>
+      </c>
+      <c r="C24" s="18">
+        <v>44572</v>
+      </c>
+      <c r="D24" s="3">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>26.297978147991028</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>83.555030132529765</v>
+        <v>0.96161313509105339</v>
       </c>
       <c r="H24">
-        <v>52.635236342296423</v>
+        <v>23.964656258597035</v>
       </c>
       <c r="I24">
-        <v>0.48012222161367712</v>
+        <v>469.12717995209761</v>
       </c>
       <c r="J24">
-        <v>13.560878679756133</v>
+        <v>41.903309867642157</v>
       </c>
       <c r="K24">
-        <v>159.00437811922646</v>
+        <v>0.63607330014090313</v>
       </c>
       <c r="L24">
-        <v>201.55003627239822</v>
+        <v>9.1039868773002333</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>125.28663377666911</v>
       </c>
       <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+        <v>170.20697097150486</v>
+      </c>
+      <c r="O24" s="18">
+        <v>44572</v>
+      </c>
+      <c r="P24">
+        <v>8</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>136</v>
+      </c>
+      <c r="R24">
+        <f>((3*5)+(1*1)+(4*2))/P24</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>0.93411780636498165</v>
+        <v>17</v>
+      </c>
+      <c r="C25" s="18">
+        <v>44589</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>7.0775871547635152</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>65.932761359164886</v>
+        <v>0.80702183651452364</v>
       </c>
       <c r="H25">
-        <v>86.748147771317761</v>
+        <v>10.455680618415109</v>
       </c>
       <c r="I25">
-        <v>0.78466152515311383</v>
+        <v>178.87378354518839</v>
       </c>
       <c r="J25">
-        <v>7.3467092504809255</v>
+        <v>40.299038984451677</v>
       </c>
       <c r="K25">
-        <v>136.35039159596252</v>
+        <v>0.27233494334137037</v>
       </c>
       <c r="L25">
-        <v>174.50818201290463</v>
+        <v>7.8353679661454105</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>9.4100335939093522</v>
       </c>
       <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>13.389546649879703</v>
+      </c>
+      <c r="O25" s="18">
+        <v>44589</v>
+      </c>
+      <c r="P25">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>135</v>
+      </c>
+      <c r="R25">
+        <f>((5*2)+(4*2)+(3*3))/P25</f>
+        <v>3.8571428571428572</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>0.89366146204626984</v>
+        <v>22</v>
+      </c>
+      <c r="C26" s="18">
+        <v>44603</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>16.726709874350476</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>181.52054191546878</v>
+        <v>0.92188121713274906</v>
       </c>
       <c r="H26">
-        <v>43.197281943272245</v>
+        <v>42.027593789363983</v>
       </c>
       <c r="I26">
-        <v>0.33262348710927125</v>
+        <v>186.15008319723404</v>
       </c>
       <c r="J26">
-        <v>11.767537332380073</v>
+        <v>39.633014680025624</v>
       </c>
       <c r="K26">
-        <v>21.7520704421615</v>
+        <v>0.32814841295460101</v>
       </c>
       <c r="L26">
-        <v>26.353884770157411</v>
+        <v>11.031716815464861</v>
       </c>
       <c r="M26">
+        <v>105.33504986099311</v>
+      </c>
+      <c r="N26">
+        <v>122.79761862196219</v>
+      </c>
+      <c r="O26" s="18">
+        <v>44603</v>
+      </c>
+      <c r="P26">
         <v>1</v>
       </c>
-      <c r="N26">
+      <c r="Q26">
         <v>1</v>
       </c>
-      <c r="O26">
+      <c r="R26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27">
+        <v>71</v>
+      </c>
+      <c r="C27" s="17">
+        <v>44606</v>
+      </c>
+      <c r="D27" s="3">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27">
         <v>2</v>
       </c>
-      <c r="E27">
-        <v>0.88084948543585173</v>
-      </c>
-      <c r="F27">
-        <v>28.204916533395153</v>
-      </c>
       <c r="G27">
-        <v>289.46023750181877</v>
+        <v>0.76182168425168695</v>
       </c>
       <c r="H27">
-        <v>53.705645309763199</v>
+        <v>49.075023070080348</v>
       </c>
       <c r="I27">
-        <v>0.44298927093214113</v>
-      </c>
-      <c r="J27">
-        <v>11.393132915155682</v>
-      </c>
-      <c r="K27">
-        <v>41.78102589694803</v>
-      </c>
-      <c r="L27">
-        <v>111.76200703682701</v>
-      </c>
-      <c r="M27">
+        <v>139.64951763061828</v>
+      </c>
+      <c r="J27" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L27" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27" t="s">
+        <v>121</v>
+      </c>
+      <c r="N27" t="s">
+        <v>121</v>
+      </c>
+      <c r="O27" s="17"/>
+      <c r="P27">
         <v>1</v>
       </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q27">
+        <v>5</v>
+      </c>
+      <c r="R27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28">
+        <v>72</v>
+      </c>
+      <c r="C28" s="17">
+        <v>44607</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28">
         <v>2</v>
       </c>
-      <c r="E28">
-        <v>0.86536802145215086</v>
-      </c>
-      <c r="F28">
-        <v>20.795897804959665</v>
-      </c>
       <c r="G28">
-        <v>61.336338232269597</v>
+        <v>0.89073325978086304</v>
       </c>
       <c r="H28">
-        <v>77.776681989483095</v>
+        <v>26.297978147991028</v>
       </c>
       <c r="I28">
-        <v>0.32887870460706831</v>
+        <v>83.555030132529765</v>
       </c>
       <c r="J28">
-        <v>21.817958441671976</v>
+        <v>52.635236342296423</v>
       </c>
       <c r="K28">
-        <v>63.694457909015462</v>
+        <v>0.48012222161367712</v>
       </c>
       <c r="L28">
-        <v>121.65943856354582</v>
+        <v>13.560878679756133</v>
       </c>
       <c r="M28">
-        <v>10</v>
-      </c>
-      <c r="N28" t="s">
-        <v>140</v>
-      </c>
-      <c r="O28">
-        <f>(1*10)/M28</f>
+        <v>159.00437811922646</v>
+      </c>
+      <c r="N28">
+        <v>201.55003627239822</v>
+      </c>
+      <c r="O28" s="17">
+        <v>44607</v>
+      </c>
+      <c r="P28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29">
+        <v>16</v>
+      </c>
+      <c r="C29" s="18">
+        <v>44608</v>
+      </c>
+      <c r="D29" s="3">
+        <v>5</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E29">
-        <v>0.9162235079877068</v>
-      </c>
       <c r="F29">
-        <v>24.545744470135475</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>61.937779563104371</v>
+        <v>0.9279084140152204</v>
       </c>
       <c r="H29">
-        <v>173.89847383049559</v>
+        <v>48.102592972145246</v>
       </c>
       <c r="I29">
-        <v>1.0827120164312798</v>
+        <v>219.37686437793496</v>
       </c>
       <c r="J29">
-        <v>19.315274981928059</v>
+        <v>57.652621836731157</v>
       </c>
       <c r="K29">
-        <v>136.73734233042214</v>
+        <v>0.5398836848281815</v>
       </c>
       <c r="L29">
-        <v>156.07035135394165</v>
+        <v>9.9502613620541265</v>
       </c>
       <c r="M29">
-        <v>5</v>
-      </c>
-      <c r="N29" t="s">
-        <v>133</v>
-      </c>
-      <c r="O29">
+        <v>112.65266362091219</v>
+      </c>
+      <c r="N29">
+        <v>91.912710611649771</v>
+      </c>
+      <c r="O29" s="18">
+        <v>44608</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>134</v>
+      </c>
+      <c r="R29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30">
+        <v>81</v>
+      </c>
+      <c r="C30" s="17">
+        <v>44612</v>
+      </c>
+      <c r="D30" s="3">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30">
         <v>2</v>
       </c>
-      <c r="E30">
-        <v>0.8763828636338783</v>
-      </c>
-      <c r="F30">
-        <v>12.79266909986408</v>
-      </c>
       <c r="G30">
-        <v>44.383724815034029</v>
+        <v>1.029700689141007</v>
       </c>
       <c r="H30">
-        <v>48.063124119531857</v>
+        <v>13.487810021148949</v>
       </c>
       <c r="I30">
-        <v>0.25528721534446464</v>
+        <v>180.02756940358057</v>
       </c>
       <c r="J30">
-        <v>27.042002636147195</v>
+        <v>52.982528683786938</v>
       </c>
       <c r="K30">
-        <v>16.096262547244134</v>
+        <v>0.70355394004385652</v>
       </c>
       <c r="L30">
-        <v>35.592166881550789</v>
+        <v>11.931708235258521</v>
       </c>
       <c r="M30">
-        <v>6</v>
-      </c>
-      <c r="N30" t="s">
-        <v>138</v>
-      </c>
-      <c r="O30">
+        <v>110.58649355921455</v>
+      </c>
+      <c r="N30">
+        <v>93.972518031999115</v>
+      </c>
+      <c r="O30" s="17">
+        <v>44612</v>
+      </c>
+      <c r="P30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31">
+        <v>74</v>
+      </c>
+      <c r="C31" s="17">
+        <v>44619</v>
+      </c>
+      <c r="D31" s="3">
+        <v>5</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31">
         <v>2</v>
       </c>
-      <c r="E31">
-        <v>0.82943994592263348</v>
-      </c>
-      <c r="F31">
-        <v>9.1531551300475531</v>
-      </c>
       <c r="G31">
-        <v>32.173873045758981</v>
+        <v>0.89366146204626984</v>
       </c>
       <c r="H31">
-        <v>103.26174930766932</v>
+        <v>16.726709874350476</v>
       </c>
       <c r="I31">
-        <v>0.22714613772822062</v>
+        <v>181.52054191546878</v>
       </c>
       <c r="J31">
-        <v>9.9785579303476677</v>
+        <v>43.197281943272245</v>
       </c>
       <c r="K31">
-        <v>9.8085980896599594</v>
+        <v>0.33262348710927125</v>
       </c>
       <c r="L31">
-        <v>20.539170496042239</v>
+        <v>11.767537332380073</v>
       </c>
       <c r="M31">
+        <v>21.7520704421615</v>
+      </c>
+      <c r="N31">
+        <v>26.353884770157411</v>
+      </c>
+      <c r="O31" s="17">
+        <v>44619</v>
+      </c>
+      <c r="P31">
         <v>1</v>
       </c>
-      <c r="N31">
+      <c r="Q31">
         <v>1</v>
       </c>
-      <c r="O31">
+      <c r="R31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32">
+        <v>75</v>
+      </c>
+      <c r="C32" s="17">
+        <v>44620</v>
+      </c>
+      <c r="D32" s="3">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32">
         <v>2</v>
       </c>
-      <c r="E32">
-        <v>1.0131888115815226</v>
-      </c>
-      <c r="F32">
-        <v>15.618540947397582</v>
-      </c>
       <c r="G32">
-        <v>131.61087062204709</v>
+        <v>0.88084948543585173</v>
       </c>
       <c r="H32">
-        <v>41.18692741298365</v>
+        <v>28.204916533395153</v>
       </c>
       <c r="I32">
-        <v>0.64119494484706341</v>
+        <v>289.46023750181877</v>
       </c>
       <c r="J32">
-        <v>10.685825516912322</v>
+        <v>53.705645309763199</v>
       </c>
       <c r="K32">
-        <v>107.18206794110587</v>
+        <v>0.44298927093214113</v>
       </c>
       <c r="L32">
-        <v>143.08753497233951</v>
+        <v>11.393132915155682</v>
       </c>
       <c r="M32">
-        <v>8</v>
-      </c>
-      <c r="N32" t="s">
-        <v>141</v>
-      </c>
-      <c r="O32">
+        <v>41.78102589694803</v>
+      </c>
+      <c r="N32">
+        <v>111.76200703682701</v>
+      </c>
+      <c r="O32" s="17">
+        <v>44620</v>
+      </c>
+      <c r="P32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33">
+        <v>65</v>
+      </c>
+      <c r="C33" s="17">
+        <v>44622</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="E33">
-        <v>1.029700689141007</v>
-      </c>
-      <c r="F33">
-        <v>13.487810021148949</v>
-      </c>
       <c r="G33">
-        <v>180.02756940358057</v>
+        <v>0.72199635922676897</v>
       </c>
       <c r="H33">
-        <v>52.982528683786938</v>
+        <v>27.097383191755213</v>
       </c>
       <c r="I33">
-        <v>0.70355394004385652</v>
-      </c>
-      <c r="J33">
-        <v>11.931708235258521</v>
-      </c>
-      <c r="K33">
-        <v>110.58649355921455</v>
-      </c>
-      <c r="L33">
-        <v>93.972518031999115</v>
-      </c>
-      <c r="M33">
+        <v>277.34523327873609</v>
+      </c>
+      <c r="J33" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" t="s">
+        <v>121</v>
+      </c>
+      <c r="M33" t="s">
+        <v>121</v>
+      </c>
+      <c r="N33" t="s">
+        <v>121</v>
+      </c>
+      <c r="O33" s="17"/>
+      <c r="P33">
         <v>1</v>
       </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33">
+        <v>2</v>
+      </c>
+      <c r="R33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34">
-        <v>0.93919756584407754</v>
+        <v>14</v>
+      </c>
+      <c r="C34" s="18">
+        <v>44623</v>
+      </c>
+      <c r="D34" s="3">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>22.187098222622993</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>232.81284658384095</v>
+        <v>0.86501924334796854</v>
       </c>
       <c r="H34">
-        <v>40.850015817504392</v>
+        <v>35.748985570739016</v>
       </c>
       <c r="I34">
-        <v>0.66836608660612418</v>
+        <v>395.46611857587158</v>
       </c>
       <c r="J34">
-        <v>25.3112561871514</v>
+        <v>57.563021246709916</v>
       </c>
       <c r="K34">
-        <v>70.140545151448066</v>
+        <v>1.2318368301159066</v>
       </c>
       <c r="L34">
-        <v>70.280899721910259</v>
+        <v>25.513000106482657</v>
       </c>
       <c r="M34">
-        <v>10</v>
-      </c>
-      <c r="N34" t="s">
-        <v>143</v>
-      </c>
-      <c r="O34">
-        <f>((1*4)+(2*6))/10</f>
-        <v>1.6</v>
-      </c>
-      <c r="P34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+        <v>272.54910509264789</v>
+      </c>
+      <c r="N34">
+        <v>314.18405452370484</v>
+      </c>
+      <c r="O34" s="18">
+        <v>44623</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <v>4</v>
+      </c>
+      <c r="R34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35">
+        <v>68</v>
+      </c>
+      <c r="C35" s="17">
+        <v>44625</v>
+      </c>
+      <c r="D35" s="3">
+        <v>5</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35">
         <v>2</v>
       </c>
-      <c r="E35">
-        <v>0.83825396406271191</v>
-      </c>
-      <c r="F35">
-        <v>79.565372082083343</v>
-      </c>
       <c r="G35">
-        <v>310.58409849330383</v>
+        <v>0.71925333016162252</v>
       </c>
       <c r="H35">
-        <v>51.97966949576584</v>
+        <v>31.627582864321159</v>
       </c>
       <c r="I35">
-        <v>1.187180700809771</v>
-      </c>
-      <c r="J35">
-        <v>51.782563142503037</v>
-      </c>
-      <c r="K35">
-        <v>386.60748366088694</v>
-      </c>
-      <c r="L35">
-        <v>588.26064575105306</v>
-      </c>
-      <c r="M35">
-        <v>22</v>
+        <v>262.70779801455848</v>
+      </c>
+      <c r="J35" t="s">
+        <v>121</v>
+      </c>
+      <c r="K35" t="s">
+        <v>121</v>
+      </c>
+      <c r="L35" t="s">
+        <v>121</v>
+      </c>
+      <c r="M35" t="s">
+        <v>121</v>
       </c>
       <c r="N35" t="s">
-        <v>149</v>
-      </c>
-      <c r="O35">
-        <v>2</v>
-      </c>
-      <c r="P35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="O35" s="17"/>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>5</v>
+      </c>
+      <c r="R35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36">
+        <v>69</v>
+      </c>
+      <c r="C36" s="17">
+        <v>44626</v>
+      </c>
+      <c r="D36" s="3">
+        <v>5</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36">
         <v>2</v>
       </c>
-      <c r="E36">
-        <v>0.90431285410188522</v>
-      </c>
-      <c r="F36">
-        <v>27.000145839646486</v>
-      </c>
       <c r="G36">
-        <v>184.55978829978042</v>
+        <v>0.85938488401942481</v>
       </c>
       <c r="H36">
-        <v>35.304299846378434</v>
+        <v>27.654924218398499</v>
       </c>
       <c r="I36">
-        <v>0.62191082466464265</v>
-      </c>
-      <c r="J36">
-        <v>16.860920307063587</v>
-      </c>
-      <c r="K36">
-        <v>46.7958548160343</v>
-      </c>
-      <c r="L36">
-        <v>183.7360895710282</v>
-      </c>
-      <c r="M36">
-        <v>14</v>
+        <v>280.87195861435953</v>
+      </c>
+      <c r="J36" t="s">
+        <v>121</v>
+      </c>
+      <c r="K36" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" t="s">
+        <v>121</v>
+      </c>
+      <c r="M36" t="s">
+        <v>121</v>
       </c>
       <c r="N36" t="s">
-        <v>145</v>
-      </c>
-      <c r="O36">
-        <f>((2*7)+(1*6)+(3*1))/14</f>
-        <v>1.6428571428571428</v>
-      </c>
-      <c r="P36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="O36" s="17"/>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36">
+        <v>3</v>
+      </c>
+      <c r="R36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37">
+        <v>73</v>
+      </c>
+      <c r="C37" s="17">
+        <v>44638</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37">
         <v>2</v>
       </c>
-      <c r="E37">
-        <v>0.90619233447163783</v>
-      </c>
-      <c r="F37">
-        <v>60.278407692382387</v>
-      </c>
       <c r="G37">
-        <v>289.48893995925721</v>
+        <v>0.93411780636498165</v>
       </c>
       <c r="H37">
-        <v>92.398845717450115</v>
+        <v>7.0775871547635152</v>
       </c>
       <c r="I37">
-        <v>0.71666422027219223</v>
+        <v>65.932761359164886</v>
       </c>
       <c r="J37">
-        <v>18.511438084366794</v>
+        <v>86.748147771317761</v>
       </c>
       <c r="K37">
-        <v>68.829706823466779</v>
+        <v>0.78466152515311383</v>
       </c>
       <c r="L37">
-        <v>106.88888921316737</v>
+        <v>7.3467092504809255</v>
       </c>
       <c r="M37">
-        <v>14</v>
-      </c>
-      <c r="N37" t="s">
-        <v>144</v>
-      </c>
-      <c r="O37">
-        <f>((5*1)+(1*3)+(2*10))/M37</f>
-        <v>2</v>
-      </c>
-      <c r="P37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+        <v>136.35039159596252</v>
+      </c>
+      <c r="N37">
+        <v>174.50818201290463</v>
+      </c>
+      <c r="O37" s="17">
+        <v>44638</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38">
-        <v>0.95693048723895513</v>
+        <v>21</v>
+      </c>
+      <c r="C38" s="18">
+        <v>44639</v>
+      </c>
+      <c r="D38" s="3">
+        <v>5</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>17.080523833436768</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>73.156940447001503</v>
+        <v>1.035875758861204</v>
       </c>
       <c r="H38">
-        <v>29.573130556837636</v>
+        <v>6.7968407717507775</v>
       </c>
       <c r="I38">
-        <v>0.3797858517718064</v>
+        <v>133.26966325321399</v>
       </c>
       <c r="J38">
-        <v>16.380057403292973</v>
+        <v>87.803690847940175</v>
       </c>
       <c r="K38">
-        <v>38.341861069609458</v>
+        <v>0.67431164589372905</v>
       </c>
       <c r="L38">
-        <v>66.97128896449189</v>
+        <v>8.6857484126838305</v>
       </c>
       <c r="M38">
-        <v>13</v>
-      </c>
-      <c r="N38" t="s">
-        <v>146</v>
-      </c>
-      <c r="O38">
+        <v>135.8285002973293</v>
+      </c>
+      <c r="N38">
+        <v>192.74606876714873</v>
+      </c>
+      <c r="O38" s="18">
+        <v>44639</v>
+      </c>
+      <c r="P38">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>129</v>
+      </c>
+      <c r="R38">
         <v>1</v>
       </c>
-      <c r="P38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39">
+        <v>64</v>
+      </c>
+      <c r="C39" s="17">
+        <v>44640</v>
+      </c>
+      <c r="D39" s="3">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39">
         <v>2</v>
       </c>
-      <c r="E39">
-        <v>0.91621224397381784</v>
-      </c>
-      <c r="F39">
-        <v>25.058629677997317</v>
-      </c>
       <c r="G39">
-        <v>68.788490017426341</v>
+        <v>0.95926114347927749</v>
       </c>
       <c r="H39">
-        <v>58.706022354485512</v>
+        <v>12.066556365700901</v>
       </c>
       <c r="I39">
-        <v>0.48295423573591645</v>
+        <v>161.92274315291311</v>
       </c>
       <c r="J39">
-        <v>17.003137623904195</v>
+        <v>52.3487620801763</v>
       </c>
       <c r="K39">
-        <v>108.40397354403991</v>
+        <v>0.64003041011396244</v>
       </c>
       <c r="L39">
-        <v>103.39171008586746</v>
+        <v>16.514215278927544</v>
       </c>
       <c r="M39">
-        <v>19</v>
-      </c>
-      <c r="N39" t="s">
-        <v>147</v>
-      </c>
-      <c r="O39">
-        <f>((1*8)+(2*6)+(4*2)+(5)+(3*2))/19</f>
-        <v>2.0526315789473686</v>
-      </c>
-      <c r="P39" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+        <v>25.154315378283385</v>
+      </c>
+      <c r="N39">
+        <v>42.292238756116532</v>
+      </c>
+      <c r="O39" s="17">
+        <v>44640</v>
+      </c>
+      <c r="P39">
+        <v>6</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>142</v>
+      </c>
+      <c r="R39">
+        <f>((1*4)+(2*2))/P39</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40">
+        <v>80</v>
+      </c>
+      <c r="C40" s="17">
+        <v>44641</v>
+      </c>
+      <c r="D40" s="3">
+        <v>5</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F40">
         <v>2</v>
       </c>
-      <c r="E40">
-        <v>0.96133627112180253</v>
-      </c>
-      <c r="F40">
-        <v>18.017795753185347</v>
-      </c>
       <c r="G40">
-        <v>92.879600778978642</v>
+        <v>1.0131888115815226</v>
       </c>
       <c r="H40">
-        <v>43.978994852749935</v>
+        <v>15.618540947397582</v>
       </c>
       <c r="I40">
-        <v>0.43728866100165364</v>
+        <v>131.61087062204709</v>
       </c>
       <c r="J40">
-        <v>19.323630536464208</v>
+        <v>41.18692741298365</v>
       </c>
       <c r="K40">
-        <v>59.864140596331971</v>
+        <v>0.64119494484706341</v>
       </c>
       <c r="L40">
-        <v>1135.9102008285563</v>
+        <v>10.685825516912322</v>
       </c>
       <c r="M40">
-        <v>28</v>
-      </c>
-      <c r="N40" t="s">
-        <v>148</v>
-      </c>
-      <c r="O40">
-        <f>((2*5)+(1*3)+(3*20))/M40</f>
-        <v>2.6071428571428572</v>
+        <v>107.18206794110587</v>
+      </c>
+      <c r="N40">
+        <v>143.08753497233951</v>
+      </c>
+      <c r="O40" s="17">
+        <v>44641</v>
       </c>
       <c r="P40" t="s">
-        <v>123</v>
+        <v>141</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R40">
+    <sortCondition ref="E2:E40"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F3E180-2472-B84B-B94F-CEC84ABE275F}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -5841,44 +6339,50 @@
       <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>127</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -5888,44 +6392,50 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="18">
+        <v>44475</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>0.72368374488545484</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>5.1239409469326826</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>24.593890076209743</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>51.382073750158312</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>0.30552330966207991</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>18.000350203003009</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>18.908057017564776</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>30.743648026756269</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -5935,44 +6445,50 @@
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="18">
+        <v>44491</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>0.88656105008731589</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>21.274117579071415</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>34.826061251676549</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>52.508533848807922</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>0.21065496754629021</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>24.521995784066746</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>8.7833807384011191</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>10.179775574037372</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -5982,44 +6498,50 @@
       <c r="C4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="17">
+        <v>44497</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>0.82943994592263348</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>9.1531551300475531</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>32.173873045758981</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>103.26174930766932</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>0.22714613772822062</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>9.9785579303476677</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>9.8085980896599594</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>20.539170496042239</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>1</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>1</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -6029,44 +6551,50 @@
       <c r="C5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="17">
+        <v>44526</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>0.80580079156721263</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>10.874727826601507</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>38.925032797494872</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>37.09827270225238</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>0.27591285814979949</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>18.322747332495339</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>44.210126018127731</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>86.44551374776627</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -6076,44 +6604,50 @@
       <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="18">
+        <v>44527</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>0.84973561934755426</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>10.471283552733373</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>45.514254168321237</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>37.130635802367529</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>0.24353026866796124</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>17.220231271854207</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>9.3829871741436826</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>11.240396518217807</v>
       </c>
-      <c r="M6">
-        <v>5</v>
-      </c>
-      <c r="N6">
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -6123,44 +6657,50 @@
       <c r="C7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="17">
+        <v>44528</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0.9162235079877068</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>24.545744470135475</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>61.937779563104371</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>173.89847383049559</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>1.0827120164312798</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>19.315274981928059</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>136.73734233042214</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>156.07035135394165</v>
       </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-      <c r="N7">
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -6170,44 +6710,50 @@
       <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="18">
+        <v>44529</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>1.2222271505973339</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>11.038185180700172</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>48.536706315537195</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>96.735988018993396</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>0.29030406206297854</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>10.660638353397356</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>32.022127097341219</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>24.357999230689543</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>3</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>2.3333333333333335</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -6217,45 +6763,51 @@
       <c r="C9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="17">
+        <v>44530</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>0.86536802145215086</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>20.795897804959665</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>61.336338232269597</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>77.776681989483095</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>0.32887870460706831</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>21.817958441671976</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>63.694457909015462</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>121.65943856354582</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>10</v>
       </c>
-      <c r="N9">
-        <f>(1*10)/L9</f>
+      <c r="P9">
+        <f>(1*10)/N9</f>
         <v>8.2196664049018653E-2</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -6265,44 +6817,50 @@
       <c r="C10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="17">
+        <v>44532</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>0.8763828636338783</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>12.79266909986408</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>44.383724815034029</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>48.063124119531857</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>0.25528721534446464</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>27.042002636147195</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>16.096262547244134</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>35.592166881550789</v>
-      </c>
-      <c r="M10">
-        <v>6</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -6312,45 +6870,51 @@
       <c r="C11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="17">
+        <v>44534</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>0.96133627112180253</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>18.017795753185347</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>92.879600778978642</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>43.978994852749935</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>0.43728866100165364</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>19.323630536464208</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>59.864140596331971</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>1135.9102008285563</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>28</v>
       </c>
-      <c r="N11">
-        <f>((2*5)+(1*3)+(3*20))/L11</f>
+      <c r="P11">
+        <f>((2*5)+(1*3)+(3*20))/N11</f>
         <v>6.4265643487268889E-2</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6360,44 +6924,50 @@
       <c r="C12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="18">
+        <v>44535</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>0.87932182745812371</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>15.618258396167157</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>64.022076659602547</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>37.024975322509512</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>0.2696689918686821</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>17.070944140937719</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>41.704638382757388</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>47.584717245536574</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>9</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>3.5555555555555554</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -6407,45 +6977,51 @@
       <c r="C13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="17">
+        <v>44539</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13">
         <v>2</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>0.91621224397381784</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>25.058629677997317</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>68.788490017426341</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>58.706022354485512</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>0.48295423573591645</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>17.003137623904195</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>108.40397354403991</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>103.39171008586746</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>19</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <f>((1*8)+(2*6)+(4*2)+(5)+(3*2))/19</f>
         <v>2.0526315789473686</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -6455,44 +7031,50 @@
       <c r="C14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="17">
+        <v>44538</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
+      </c>
+      <c r="F14">
         <v>2</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>0.95693048723895513</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>17.080523833436768</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>73.156940447001503</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>29.573130556837636</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>0.3797858517718064</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>16.380057403292973</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>38.341861069609458</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>66.97128896449189</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>13</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>1</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -6502,44 +7084,50 @@
       <c r="C15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="17">
+        <v>44539</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15">
         <v>1</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>0.80933442637431929</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>8.5803896552124019</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>349.33938408922165</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>27.134223195237617</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>0.96107202444760242</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>24.006529318345894</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>23.481281407349556</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>37.824234563318797</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>4</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>1</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -6549,44 +7137,50 @@
       <c r="C16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="18">
+        <v>44543</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5</v>
+      </c>
+      <c r="F16">
         <v>1</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>0.78902058669226527</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>21.85266026837348</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>486.48239756691532</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>42.10435597115773</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>1.0102772948184773</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>28.939842343182082</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>199.02388947971676</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>192.53405332023902</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>6</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>3.4285714285714284</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -6596,45 +7190,51 @@
       <c r="C17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="17">
+        <v>44544</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>0.93919756584407754</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>22.187098222622993</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>232.81284658384095</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>40.850015817504392</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>0.66836608660612418</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>25.3112561871514</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>70.140545151448066</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>70.280899721910259</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>10</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <f>((1*4)+(2*6))/10</f>
         <v>1.6</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6644,45 +7244,51 @@
       <c r="C18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="17">
+        <v>44546</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5</v>
+      </c>
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>0.90619233447163783</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>60.278407692382387</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>289.48893995925721</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>92.398845717450115</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>0.71666422027219223</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>18.511438084366794</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>68.829706823466779</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>106.88888921316737</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>14</v>
       </c>
-      <c r="N18">
-        <f>((5*1)+(1*3)+(2*10))/L18</f>
+      <c r="P18">
+        <f>((5*1)+(1*3)+(2*10))/N18</f>
         <v>0.26195426115954762</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -6692,45 +7298,51 @@
       <c r="C19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="17">
+        <v>44545</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19">
         <v>2</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>0.90431285410188522</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>27.000145839646486</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>184.55978829978042</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>35.304299846378434</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>0.62191082466464265</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>16.860920307063587</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>46.7958548160343</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>183.7360895710282</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>14</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <f>((2*7)+(1*6)+(3*1))/14</f>
         <v>1.6428571428571428</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -6740,44 +7352,50 @@
       <c r="C20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="17">
+        <v>44549</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>0.83825396406271191</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>79.565372082083343</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>310.58409849330383</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>51.97966949576584</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>1.187180700809771</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>51.782563142503037</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>386.60748366088694</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>588.26064575105306</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>22</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>2</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -6787,44 +7405,50 @@
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="18">
+        <v>44572</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5</v>
+      </c>
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>0.96161313509105339</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>23.964656258597035</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>469.12717995209761</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>41.903309867642157</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>0.63607330014090313</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>9.1039868773002333</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>125.28663377666911</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>170.20697097150486</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>8</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>3</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -6834,44 +7458,50 @@
       <c r="C22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="18">
+        <v>44589</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5</v>
+      </c>
+      <c r="F22">
         <v>1</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>0.80702183651452364</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>10.455680618415109</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>178.87378354518839</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>40.299038984451677</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>0.27233494334137037</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>7.8353679661454105</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>9.4100335939093522</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>13.389546649879703</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>7</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>3.8571428571428572</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -6881,44 +7511,50 @@
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="18">
+        <v>44603</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5</v>
+      </c>
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>0.92188121713274906</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>42.027593789363983</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>186.15008319723404</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>39.633014680025624</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>0.32814841295460101</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>11.031716815464861</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>105.33504986099311</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>122.79761862196219</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>1</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>1</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -6928,44 +7564,50 @@
       <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="17">
+        <v>44607</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>0.89073325978086304</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>26.297978147991028</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>83.555030132529765</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>52.635236342296423</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>0.48012222161367712</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>13.560878679756133</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>159.00437811922646</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>201.55003627239822</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>1</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>1</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -6975,44 +7617,50 @@
       <c r="C25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="18">
+        <v>44608</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5</v>
+      </c>
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>0.9279084140152204</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>48.102592972145246</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>219.37686437793496</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>57.652621836731157</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>0.5398836848281815</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>9.9502613620541265</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>112.65266362091219</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>91.912710611649771</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>2</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>1</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7022,44 +7670,50 @@
       <c r="C26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="17">
+        <v>44612</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26">
         <v>2</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>1.029700689141007</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>13.487810021148949</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>180.02756940358057</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>52.982528683786938</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>0.70355394004385652</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>11.931708235258521</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>110.58649355921455</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>93.972518031999115</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>1</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>1</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -7069,44 +7723,50 @@
       <c r="C27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="17">
+        <v>44619</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27">
         <v>2</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>0.89366146204626984</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>16.726709874350476</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>181.52054191546878</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>43.197281943272245</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>0.33262348710927125</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>11.767537332380073</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>21.7520704421615</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>26.353884770157411</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>1</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>1</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -7116,44 +7776,50 @@
       <c r="C28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="17">
+        <v>44620</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28">
         <v>2</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>0.88084948543585173</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>28.204916533395153</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>289.46023750181877</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>53.705645309763199</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>0.44298927093214113</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>11.393132915155682</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>41.78102589694803</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>111.76200703682701</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>1</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>1</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -7163,44 +7829,50 @@
       <c r="C29" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="18">
+        <v>44623</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+      <c r="F29">
         <v>1</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0.86501924334796854</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>35.748985570739016</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>395.46611857587158</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>57.563021246709916</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>1.2318368301159066</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>25.513000106482657</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>272.54910509264789</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>314.18405452370484</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>1</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>4</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -7210,44 +7882,50 @@
       <c r="C30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="17">
+        <v>44638</v>
+      </c>
+      <c r="E30" s="3">
+        <v>5</v>
+      </c>
+      <c r="F30">
         <v>2</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>0.93411780636498165</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>7.0775871547635152</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>65.932761359164886</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>86.748147771317761</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>0.78466152515311383</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>7.3467092504809255</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>136.35039159596252</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>174.50818201290463</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>1</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>1</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -7257,44 +7935,50 @@
       <c r="C31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="18">
+        <v>44639</v>
+      </c>
+      <c r="E31" s="3">
+        <v>5</v>
+      </c>
+      <c r="F31">
         <v>1</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>1.035875758861204</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>6.7968407717507775</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>133.26966325321399</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>87.803690847940175</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>0.67431164589372905</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>8.6857484126838305</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>135.8285002973293</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>192.74606876714873</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>4</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>1</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -7304,44 +7988,50 @@
       <c r="C32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="17">
+        <v>44640</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5</v>
+      </c>
+      <c r="F32">
         <v>2</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <v>0.95926114347927749</v>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>12.066556365700901</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>161.92274315291311</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>52.3487620801763</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>0.64003041011396244</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>16.514215278927544</v>
       </c>
-      <c r="K32">
+      <c r="M32">
         <v>25.154315378283385</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>42.292238756116532</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>6</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>1.3333333333333333</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -7351,45 +8041,51 @@
       <c r="C33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="17">
+        <v>44641</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>1.0131888115815226</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>15.618540947397582</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>131.61087062204709</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>41.18692741298365</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>0.64119494484706341</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>10.685825516912322</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>107.18206794110587</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>143.08753497233951</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>8</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>1</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P33">
     <sortCondition ref="C2:C33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10299,11 +10995,11 @@
         <f t="shared" ref="G6:I6" si="0">G3/G4</f>
         <v>0.27926256519369991</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="16">
         <f t="shared" si="0"/>
         <v>0.99028293798228051</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="16">
         <f t="shared" si="0"/>
         <v>0.92844919999733633</v>
       </c>
@@ -10311,7 +11007,7 @@
         <f>K3/K4</f>
         <v>0.6135710517729791</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="15">
         <f t="shared" ref="L6:R6" si="1">L3/L4</f>
         <v>3.8364748306497343</v>
       </c>
@@ -10319,7 +11015,7 @@
         <f t="shared" si="1"/>
         <v>0.6807280758188643</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="14">
         <f t="shared" si="1"/>
         <v>2.5799726110739645</v>
       </c>
@@ -10327,15 +11023,15 @@
         <f t="shared" si="1"/>
         <v>0.46615858868787163</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="16">
         <f t="shared" si="1"/>
         <v>1.1178068564743366</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6">
         <f t="shared" si="1"/>
         <v>3.2215717994082183</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="14">
         <f t="shared" si="1"/>
         <v>2.4398211267921601</v>
       </c>
@@ -10344,15 +11040,15 @@
       <c r="A8" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="10">
         <f>D4/D5</f>
         <v>1.0438596491228072</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <f t="shared" ref="E8:I8" si="2">E4/E5</f>
         <v>1.0412979351032448</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <f t="shared" si="2"/>
         <v>1.1010928961748634</v>
       </c>
@@ -10360,15 +11056,15 @@
         <f t="shared" si="2"/>
         <v>1.3340083161342524</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="10">
         <f t="shared" si="2"/>
         <v>0.99914334665905191</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="10">
         <f t="shared" si="2"/>
         <v>1.0002997162685994</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="10">
         <f>K4/K5</f>
         <v>0.91285653129109656</v>
       </c>
@@ -10376,11 +11072,11 @@
         <f t="shared" ref="L8:R8" si="3">L4/L5</f>
         <v>1356.7629973873836</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="13">
         <f t="shared" si="3"/>
         <v>8.3321161983457709E-2</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="13">
         <f t="shared" si="3"/>
         <v>6.6930533651232554E-2</v>
       </c>
@@ -10401,7 +11097,7 @@
       <c r="A10" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <f>D3/D5</f>
         <v>0.44736842105263164</v>
       </c>
@@ -10409,7 +11105,7 @@
         <f t="shared" ref="E10:I10" si="4">E3/E5</f>
         <v>0.21238938053097345</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <f t="shared" si="4"/>
         <v>0.46448087431693985</v>
       </c>
@@ -10425,7 +11121,7 @@
         <f t="shared" si="4"/>
         <v>0.92872747132714362</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="11">
         <f>K3/K5</f>
         <v>0.56010234202211151</v>
       </c>
@@ -10433,11 +11129,11 @@
         <f t="shared" ref="L10:R10" si="5">L3/L5</f>
         <v>5205.1870906335889</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="12">
         <f t="shared" si="5"/>
         <v>5.6719054271991073E-2</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="12">
         <f t="shared" si="5"/>
         <v>3.1200243106984663E-2</v>
       </c>

--- a/Pteropod_summary_MeCa.xlsx
+++ b/Pteropod_summary_MeCa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clairesheppard/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD36991-2FA6-7C48-B28B-E0E5A8DC7B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0DC08F-3781-6540-9987-2344CBEBC6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="1480" windowWidth="28700" windowHeight="16440" activeTab="1" xr2:uid="{8C9521DA-CBBE-964C-8613-3A9834640F7F}"/>
+    <workbookView xWindow="60" yWindow="1480" windowWidth="28700" windowHeight="16440" activeTab="2" xr2:uid="{8C9521DA-CBBE-964C-8613-3A9834640F7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="203">
   <si>
     <t>12-4</t>
   </si>
@@ -624,13 +624,53 @@
   </si>
   <si>
     <t xml:space="preserve">number </t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -671,6 +711,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="3"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1087,9 +1132,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8211D348-F208-774D-8E83-1DF297E35079}">
   <dimension ref="A1:AB88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -1133,7 +1178,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1175,7 +1220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1217,7 +1262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1259,7 +1304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1301,7 +1346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1343,7 +1388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1385,7 +1430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1427,7 +1472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1469,7 +1514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1511,7 +1556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1553,7 +1598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1595,7 +1640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1637,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -1679,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1721,7 +1766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -1798,7 +1843,7 @@
         <v>513.90317393468467</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -1875,7 +1920,7 @@
         <v>627.11718748768214</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1954,7 +1999,7 @@
         <v>548.66957616592072</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -2033,7 +2078,7 @@
         <v>219.93697957266215</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -2112,7 +2157,7 @@
         <v>156.34316228209411</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -2191,7 +2236,7 @@
         <v>141.92032139848197</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2270,7 +2315,7 @@
         <v>72.380084089451174</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -2349,7 +2394,7 @@
         <v>53.637733087144142</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2428,7 +2473,7 @@
         <v>59.876917988874879</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2507,7 +2552,7 @@
         <v>45.282253824305165</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2586,7 +2631,7 @@
         <v>62.512748584023385</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -2665,7 +2710,7 @@
         <v>46.069786166823988</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -2707,7 +2752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2731,7 +2776,7 @@
         <v>277.34523327873609</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -2787,7 +2832,7 @@
         <v>61.964911721823398</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2811,7 +2856,7 @@
         <v>43.484155321149728</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2835,7 +2880,7 @@
         <v>262.70779801455848</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2859,7 +2904,7 @@
         <v>280.87195861435953</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2883,7 +2928,7 @@
         <v>19.586506653739349</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2907,7 +2952,7 @@
         <v>139.64951763061828</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -2949,7 +2994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -2991,7 +3036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -3033,7 +3078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -3075,7 +3120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -3117,7 +3162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -3159,7 +3204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -3201,7 +3246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -3243,7 +3288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -3285,7 +3330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -3327,7 +3372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -3369,7 +3414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -3411,7 +3456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>33</v>
       </c>
@@ -3453,7 +3498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -3495,7 +3540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>33</v>
       </c>
@@ -3537,7 +3582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>33</v>
       </c>
@@ -3579,7 +3624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>33</v>
       </c>
@@ -3621,181 +3666,181 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14">
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14">
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14">
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14">
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14">
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14">
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14">
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:7">
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:7">
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:7">
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:7">
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:7">
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:7">
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:7">
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:7">
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:7">
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:7">
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:7">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:7">
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:7">
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:7">
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:7">
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:7">
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:7">
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:7">
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:7">
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:7">
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:7">
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:7">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:7">
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:7">
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="G88" s="1"/>
@@ -3813,9 +3858,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94A4FAE-06C3-2A4F-945E-0AABB8D779A9}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="D1" t="s">
         <v>169</v>
       </c>
@@ -3829,7 +3874,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -3883,7 +3928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -3936,7 +3981,7 @@
         <v>151.1833007387159</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -3989,7 +4034,7 @@
         <v>61.964911721823398</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -4047,16 +4092,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3F7547-7462-974B-B6A7-2E1E312B7BC2}">
-  <dimension ref="A1:S40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="14" max="14" width="15.1640625" customWidth="1"/>
-    <col min="15" max="15" width="43.33203125" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="15.1640625" customWidth="1"/>
+    <col min="16" max="16" width="43.33203125" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -4073,49 +4118,52 @@
         <v>59</v>
       </c>
       <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
         <v>114</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>122</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>128</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>127</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -4131,38 +4179,38 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.72368374488545484</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>5.1239409469326826</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>24.593890076209743</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>51.382073750158312</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.30552330966207991</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>18.000350203003009</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>18.908057017564776</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>30.743648026756269</v>
       </c>
-      <c r="O2" s="18">
-        <v>5</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
+      <c r="P2" s="18">
+        <v>5</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -4170,8 +4218,11 @@
       <c r="R2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -4187,38 +4238,38 @@
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.88656105008731589</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>21.274117579071415</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>34.826061251676549</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>52.508533848807922</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.21065496754629021</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>24.521995784066746</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>8.7833807384011191</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>10.179775574037372</v>
       </c>
-      <c r="O3" s="18">
+      <c r="P3" s="18">
         <v>44491</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -4226,8 +4277,11 @@
       <c r="R3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -4243,20 +4297,20 @@
       <c r="E4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.81336733202131484</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>21.186105772811882</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>15.801180336692479</v>
-      </c>
-      <c r="J4" t="s">
-        <v>121</v>
       </c>
       <c r="K4" t="s">
         <v>121</v>
@@ -4270,18 +4324,21 @@
       <c r="N4" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="17"/>
-      <c r="P4">
-        <v>1</v>
-      </c>
+      <c r="O4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P4" s="17"/>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -4297,20 +4354,20 @@
       <c r="E5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.87057806018547423</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>16.354827881837799</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>19.586506653739349</v>
-      </c>
-      <c r="J5" t="s">
-        <v>121</v>
       </c>
       <c r="K5" t="s">
         <v>121</v>
@@ -4324,18 +4381,21 @@
       <c r="N5" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5">
-        <v>1</v>
-      </c>
+      <c r="O5" t="s">
+        <v>121</v>
+      </c>
+      <c r="P5" s="17"/>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4351,38 +4411,38 @@
       <c r="E6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.82943994592263348</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>9.1531551300475531</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>32.173873045758981</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>103.26174930766932</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.22714613772822062</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>9.9785579303476677</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>9.8085980896599594</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>20.539170496042239</v>
       </c>
-      <c r="O6" s="17">
+      <c r="P6" s="17">
         <v>44497</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4390,8 +4450,11 @@
       <c r="R6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -4407,48 +4470,51 @@
       <c r="E7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.80580079156721263</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>10.874727826601507</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>38.925032797494872</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>37.09827270225238</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.27591285814979949</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>18.322747332495339</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>44.210126018127731</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>86.44551374776627</v>
       </c>
-      <c r="O7" s="17">
+      <c r="P7" s="17">
         <v>44526</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>4</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>130</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f>(4*1)/1</f>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -4464,48 +4530,51 @@
       <c r="E8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.84973561934755426</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>10.471283552733373</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>45.514254168321237</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>37.130635802367529</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.24353026866796124</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>17.220231271854207</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>9.3829871741436826</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>11.240396518217807</v>
       </c>
-      <c r="O8" s="18">
+      <c r="P8" s="18">
         <v>44527</v>
       </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="Q8">
+        <v>5</v>
+      </c>
+      <c r="R8" t="s">
         <v>133</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f>(1*5)/5</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -4521,47 +4590,50 @@
       <c r="E9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.9162235079877068</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>24.545744470135475</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>61.937779563104371</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>173.89847383049559</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1.0827120164312798</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>19.315274981928059</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>136.73734233042214</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>156.07035135394165</v>
       </c>
-      <c r="O9" s="17">
+      <c r="P9" s="17">
         <v>44528</v>
       </c>
-      <c r="P9">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9" t="s">
         <v>133</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -4577,48 +4649,51 @@
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1.2222271505973339</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>11.038185180700172</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>48.536706315537195</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>96.735988018993396</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.29030406206297854</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>10.660638353397356</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>32.022127097341219</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>24.357999230689543</v>
       </c>
-      <c r="O10" s="18">
+      <c r="P10" s="18">
         <v>44529</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>3</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>137</v>
       </c>
-      <c r="R10">
-        <f>((3)+(2*2))/P10</f>
+      <c r="S10">
+        <f>((3)+(2*2))/Q10</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -4634,48 +4709,51 @@
       <c r="E11" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.86536802145215086</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>20.795897804959665</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>61.336338232269597</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>77.776681989483095</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.32887870460706831</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>21.817958441671976</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>63.694457909015462</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>121.65943856354582</v>
       </c>
-      <c r="O11" s="17">
+      <c r="P11" s="17">
         <v>44530</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>10</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>140</v>
       </c>
-      <c r="R11">
-        <f>(1*10)/P11</f>
+      <c r="S11">
+        <f>(1*10)/Q11</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -4691,20 +4769,20 @@
       <c r="E12" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.77073714592290399</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>18.418874611647716</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>43.484155321149728</v>
-      </c>
-      <c r="J12" t="s">
-        <v>121</v>
       </c>
       <c r="K12" t="s">
         <v>121</v>
@@ -4718,19 +4796,22 @@
       <c r="N12" t="s">
         <v>121</v>
       </c>
-      <c r="O12" s="17"/>
-      <c r="P12">
+      <c r="O12" t="s">
+        <v>121</v>
+      </c>
+      <c r="P12" s="17"/>
+      <c r="Q12">
         <v>3</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>139</v>
       </c>
-      <c r="R12">
-        <f>((3*1)+(1*2))/P12</f>
+      <c r="S12">
+        <f>((3*1)+(1*2))/Q12</f>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -4746,47 +4827,50 @@
       <c r="E13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13">
         <v>2</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.8763828636338783</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>12.79266909986408</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>44.383724815034029</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>48.063124119531857</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.25528721534446464</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>27.042002636147195</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>16.096262547244134</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>35.592166881550789</v>
       </c>
-      <c r="O13" s="17">
+      <c r="P13" s="17">
         <v>44532</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>138</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -4802,51 +4886,54 @@
       <c r="E14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14">
         <v>2</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.96133627112180253</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>18.017795753185347</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>92.879600778978642</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>43.978994852749935</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.43728866100165364</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>19.323630536464208</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>59.864140596331971</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>1135.9102008285563</v>
       </c>
-      <c r="O14" s="17">
+      <c r="P14" s="17">
         <v>44534</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>28</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>148</v>
       </c>
-      <c r="R14">
-        <f>((2*5)+(1*3)+(3*20))/P14</f>
+      <c r="S14">
+        <f>((2*5)+(1*3)+(3*20))/Q14</f>
         <v>2.6071428571428572</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -4862,48 +4949,51 @@
       <c r="E15" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.87932182745812371</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>15.618258396167157</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>64.022076659602547</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>37.024975322509512</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.2696689918686821</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>17.070944140937719</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>41.704638382757388</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>47.584717245536574</v>
       </c>
-      <c r="O15" s="18">
+      <c r="P15" s="18">
         <v>44535</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>9</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>132</v>
       </c>
-      <c r="R15">
-        <f>((5*4)+(4*2)+(1*2)+2)/P15</f>
+      <c r="S15">
+        <f>((5*4)+(4*2)+(1*2)+2)/Q15</f>
         <v>3.5555555555555554</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -4919,51 +5009,54 @@
       <c r="E16" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G16">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.91621224397381784</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>25.058629677997317</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>68.788490017426341</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>58.706022354485512</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.48295423573591645</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>17.003137623904195</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>108.40397354403991</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>103.39171008586746</v>
       </c>
-      <c r="O16" s="17">
+      <c r="P16" s="17">
         <v>44539</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>19</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>147</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <f>((1*8)+(2*6)+(4*2)+(5)+(3*2))/19</f>
         <v>2.0526315789473686</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -4979,50 +5072,53 @@
       <c r="E17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G17">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.95693048723895513</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>17.080523833436768</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>73.156940447001503</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>29.573130556837636</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.3797858517718064</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>16.380057403292973</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>38.341861069609458</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>66.97128896449189</v>
       </c>
-      <c r="O17" s="17">
+      <c r="P17" s="17">
         <v>44538</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>13</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>146</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>1</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -5038,48 +5134,51 @@
       <c r="E18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.80933442637431929</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>8.5803896552124019</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>349.33938408922165</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>27.134223195237617</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.96107202444760242</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>24.006529318345894</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>23.481281407349556</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>37.824234563318797</v>
       </c>
-      <c r="O18" s="17">
+      <c r="P18" s="17">
         <v>44539</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>4</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>129</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f>(1*4)/4</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -5095,48 +5194,51 @@
       <c r="E19" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.78902058669226527</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>21.85266026837348</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>486.48239756691532</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>42.10435597115773</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>1.0102772948184773</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>28.939842343182082</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>199.02388947971676</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>192.53405332023902</v>
       </c>
-      <c r="O19" s="18">
+      <c r="P19" s="18">
         <v>44543</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>7</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>131</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f>((3*3)+(2*1)+(5)+(4*2))/7</f>
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -5152,51 +5254,54 @@
       <c r="E20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.93919756584407754</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>22.187098222622993</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>232.81284658384095</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>40.850015817504392</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.66836608660612418</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>25.3112561871514</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>70.140545151448066</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>70.280899721910259</v>
       </c>
-      <c r="O20" s="17">
+      <c r="P20" s="17">
         <v>44544</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>10</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>143</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f>((1*4)+(2*6))/10</f>
         <v>1.6</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -5212,51 +5317,54 @@
       <c r="E21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21">
         <v>2</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.90619233447163783</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>60.278407692382387</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>289.48893995925721</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>92.398845717450115</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.71666422027219223</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>18.511438084366794</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>68.829706823466779</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>106.88888921316737</v>
       </c>
-      <c r="O21" s="17">
+      <c r="P21" s="17">
         <v>44546</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>14</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>144</v>
       </c>
-      <c r="R21">
-        <f>((5*1)+(1*3)+(2*10))/P21</f>
+      <c r="S21">
+        <f>((5*1)+(1*3)+(2*10))/Q21</f>
         <v>2</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -5272,51 +5380,54 @@
       <c r="E22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G22">
         <v>2</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.90431285410188522</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>27.000145839646486</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>184.55978829978042</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>35.304299846378434</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.62191082466464265</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>16.860920307063587</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>46.7958548160343</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>183.7360895710282</v>
       </c>
-      <c r="O22" s="17">
+      <c r="P22" s="17">
         <v>44545</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>14</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>145</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f>((2*7)+(1*6)+(3*1))/14</f>
         <v>1.6428571428571428</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -5332,50 +5443,53 @@
       <c r="E23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23">
         <v>2</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.83825396406271191</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>79.565372082083343</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>310.58409849330383</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>51.97966949576584</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>1.187180700809771</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>51.782563142503037</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>386.60748366088694</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>588.26064575105306</v>
       </c>
-      <c r="O23" s="17">
+      <c r="P23" s="17">
         <v>44549</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>22</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>149</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>2</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -5391,48 +5505,51 @@
       <c r="E24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>0.96161313509105339</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>23.964656258597035</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>469.12717995209761</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>41.903309867642157</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.63607330014090313</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>9.1039868773002333</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>125.28663377666911</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>170.20697097150486</v>
       </c>
-      <c r="O24" s="18">
+      <c r="P24" s="18">
         <v>44572</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>8</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>136</v>
       </c>
-      <c r="R24">
-        <f>((3*5)+(1*1)+(4*2))/P24</f>
+      <c r="S24">
+        <f>((3*5)+(1*1)+(4*2))/Q24</f>
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -5448,48 +5565,51 @@
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.80702183651452364</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>10.455680618415109</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>178.87378354518839</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>40.299038984451677</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0.27233494334137037</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>7.8353679661454105</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>9.4100335939093522</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>13.389546649879703</v>
       </c>
-      <c r="O25" s="18">
+      <c r="P25" s="18">
         <v>44589</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>7</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>135</v>
       </c>
-      <c r="R25">
-        <f>((5*2)+(4*2)+(3*3))/P25</f>
+      <c r="S25">
+        <f>((5*2)+(4*2)+(3*3))/Q25</f>
         <v>3.8571428571428572</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -5505,38 +5625,38 @@
       <c r="E26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.92188121713274906</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>42.027593789363983</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>186.15008319723404</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>39.633014680025624</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>0.32814841295460101</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>11.031716815464861</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>105.33504986099311</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>122.79761862196219</v>
       </c>
-      <c r="O26" s="18">
+      <c r="P26" s="18">
         <v>44603</v>
-      </c>
-      <c r="P26">
-        <v>1</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -5544,8 +5664,11 @@
       <c r="R26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -5561,20 +5684,20 @@
       <c r="E27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27">
         <v>2</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>0.76182168425168695</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>49.075023070080348</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>139.64951763061828</v>
-      </c>
-      <c r="J27" t="s">
-        <v>121</v>
       </c>
       <c r="K27" t="s">
         <v>121</v>
@@ -5588,18 +5711,21 @@
       <c r="N27" t="s">
         <v>121</v>
       </c>
-      <c r="O27" s="17"/>
-      <c r="P27">
+      <c r="O27" t="s">
+        <v>121</v>
+      </c>
+      <c r="P27" s="17"/>
+      <c r="Q27">
         <v>1</v>
       </c>
-      <c r="Q27">
-        <v>5</v>
-      </c>
       <c r="R27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -5615,38 +5741,38 @@
       <c r="E28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28">
         <v>2</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.89073325978086304</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>26.297978147991028</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>83.555030132529765</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>52.635236342296423</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>0.48012222161367712</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>13.560878679756133</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>159.00437811922646</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>201.55003627239822</v>
       </c>
-      <c r="O28" s="17">
+      <c r="P28" s="17">
         <v>44607</v>
-      </c>
-      <c r="P28">
-        <v>1</v>
       </c>
       <c r="Q28">
         <v>1</v>
@@ -5654,8 +5780,11 @@
       <c r="R28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -5671,47 +5800,50 @@
       <c r="E29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.9279084140152204</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>48.102592972145246</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>219.37686437793496</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>57.652621836731157</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>0.5398836848281815</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>9.9502613620541265</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>112.65266362091219</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>91.912710611649771</v>
       </c>
-      <c r="O29" s="18">
+      <c r="P29" s="18">
         <v>44608</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>2</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>134</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -5727,44 +5859,47 @@
       <c r="E30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30">
         <v>2</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1.029700689141007</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>13.487810021148949</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>180.02756940358057</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>52.982528683786938</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>0.70355394004385652</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>11.931708235258521</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>110.58649355921455</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>93.972518031999115</v>
       </c>
-      <c r="O30" s="17">
+      <c r="P30" s="17">
         <v>44612</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>1</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -5780,38 +5915,38 @@
       <c r="E31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31">
         <v>2</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.89366146204626984</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>16.726709874350476</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>181.52054191546878</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>43.197281943272245</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>0.33262348710927125</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>11.767537332380073</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>21.7520704421615</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>26.353884770157411</v>
       </c>
-      <c r="O31" s="17">
+      <c r="P31" s="17">
         <v>44619</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
       </c>
       <c r="Q31">
         <v>1</v>
@@ -5819,8 +5954,11 @@
       <c r="R31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -5836,38 +5974,38 @@
       <c r="E32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32">
         <v>2</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.88084948543585173</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>28.204916533395153</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>289.46023750181877</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>53.705645309763199</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>0.44298927093214113</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>11.393132915155682</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>41.78102589694803</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>111.76200703682701</v>
       </c>
-      <c r="O32" s="17">
+      <c r="P32" s="17">
         <v>44620</v>
-      </c>
-      <c r="P32">
-        <v>1</v>
       </c>
       <c r="Q32">
         <v>1</v>
@@ -5875,8 +6013,11 @@
       <c r="R32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -5892,20 +6033,20 @@
       <c r="E33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G33">
         <v>2</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>0.72199635922676897</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>27.097383191755213</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>277.34523327873609</v>
-      </c>
-      <c r="J33" t="s">
-        <v>121</v>
       </c>
       <c r="K33" t="s">
         <v>121</v>
@@ -5919,18 +6060,21 @@
       <c r="N33" t="s">
         <v>121</v>
       </c>
-      <c r="O33" s="17"/>
-      <c r="P33">
+      <c r="O33" t="s">
+        <v>121</v>
+      </c>
+      <c r="P33" s="17"/>
+      <c r="Q33">
         <v>1</v>
-      </c>
-      <c r="Q33">
-        <v>2</v>
       </c>
       <c r="R33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -5946,47 +6090,50 @@
       <c r="E34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G34">
         <v>1</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>0.86501924334796854</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>35.748985570739016</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>395.46611857587158</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>57.563021246709916</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>1.2318368301159066</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>25.513000106482657</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>272.54910509264789</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>314.18405452370484</v>
       </c>
-      <c r="O34" s="18">
+      <c r="P34" s="18">
         <v>44623</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>1</v>
-      </c>
-      <c r="Q34">
-        <v>4</v>
       </c>
       <c r="R34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -6002,20 +6149,20 @@
       <c r="E35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G35">
         <v>2</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>0.71925333016162252</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>31.627582864321159</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>262.70779801455848</v>
-      </c>
-      <c r="J35" t="s">
-        <v>121</v>
       </c>
       <c r="K35" t="s">
         <v>121</v>
@@ -6029,18 +6176,21 @@
       <c r="N35" t="s">
         <v>121</v>
       </c>
-      <c r="O35" s="17"/>
-      <c r="P35">
+      <c r="O35" t="s">
+        <v>121</v>
+      </c>
+      <c r="P35" s="17"/>
+      <c r="Q35">
         <v>1</v>
       </c>
-      <c r="Q35">
-        <v>5</v>
-      </c>
       <c r="R35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -6056,20 +6206,20 @@
       <c r="E36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G36">
         <v>2</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>0.85938488401942481</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>27.654924218398499</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>280.87195861435953</v>
-      </c>
-      <c r="J36" t="s">
-        <v>121</v>
       </c>
       <c r="K36" t="s">
         <v>121</v>
@@ -6083,18 +6233,21 @@
       <c r="N36" t="s">
         <v>121</v>
       </c>
-      <c r="O36" s="17"/>
-      <c r="P36">
+      <c r="O36" t="s">
+        <v>121</v>
+      </c>
+      <c r="P36" s="17"/>
+      <c r="Q36">
         <v>1</v>
-      </c>
-      <c r="Q36">
-        <v>3</v>
       </c>
       <c r="R36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -6110,38 +6263,38 @@
       <c r="E37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G37">
         <v>2</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.93411780636498165</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>7.0775871547635152</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>65.932761359164886</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>86.748147771317761</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>0.78466152515311383</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>7.3467092504809255</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>136.35039159596252</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>174.50818201290463</v>
       </c>
-      <c r="O37" s="17">
+      <c r="P37" s="17">
         <v>44638</v>
-      </c>
-      <c r="P37">
-        <v>1</v>
       </c>
       <c r="Q37">
         <v>1</v>
@@ -6149,8 +6302,11 @@
       <c r="R37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -6166,47 +6322,50 @@
       <c r="E38" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G38">
         <v>1</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>1.035875758861204</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>6.7968407717507775</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>133.26966325321399</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>87.803690847940175</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>0.67431164589372905</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>8.6857484126838305</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>135.8285002973293</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>192.74606876714873</v>
       </c>
-      <c r="O38" s="18">
+      <c r="P38" s="18">
         <v>44639</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>4</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>129</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -6222,48 +6381,51 @@
       <c r="E39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G39">
         <v>2</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>0.95926114347927749</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>12.066556365700901</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>161.92274315291311</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>52.3487620801763</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.64003041011396244</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>16.514215278927544</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>25.154315378283385</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>42.292238756116532</v>
       </c>
-      <c r="O39" s="17">
+      <c r="P39" s="17">
         <v>44640</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>6</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>142</v>
       </c>
-      <c r="R39">
-        <f>((1*4)+(2*2))/P39</f>
+      <c r="S39">
+        <f>((1*4)+(2*2))/Q39</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -6279,47 +6441,51 @@
       <c r="E40" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G40">
         <v>2</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>1.0131888115815226</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>15.618540947397582</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>131.61087062204709</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>41.18692741298365</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.64119494484706341</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>10.685825516912322</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>107.18206794110587</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>143.08753497233951</v>
       </c>
-      <c r="O40" s="17">
+      <c r="P40" s="17">
         <v>44641</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>141</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R40">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S40">
     <sortCondition ref="E2:E40"/>
   </sortState>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6327,9 +6493,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F3E180-2472-B84B-B94F-CEC84ABE275F}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -6382,7 +6548,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -6435,7 +6601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -6488,7 +6654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -6541,7 +6707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -6594,7 +6760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -6647,7 +6813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -6700,7 +6866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -6753,7 +6919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -6807,7 +6973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -6860,7 +7026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -6914,7 +7080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6967,7 +7133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -7021,7 +7187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -7074,7 +7240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -7127,7 +7293,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -7180,7 +7346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -7234,7 +7400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -7288,7 +7454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -7342,7 +7508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -7395,7 +7561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -7448,7 +7614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -7501,7 +7667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -7554,7 +7720,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -7607,7 +7773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -7660,7 +7826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7713,7 +7879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -7766,7 +7932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -7819,7 +7985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -7872,7 +8038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -7925,7 +8091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -7978,7 +8144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -8031,7 +8197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -8095,9 +8261,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27F2CE-D865-1748-84AA-14C7910A927C}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>156</v>
       </c>
@@ -8105,7 +8271,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -8137,7 +8303,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>158</v>
       </c>
@@ -8169,7 +8335,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>158</v>
       </c>
@@ -8201,7 +8367,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>158</v>
       </c>
@@ -8233,7 +8399,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -8265,7 +8431,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>161</v>
       </c>
@@ -8297,7 +8463,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>161</v>
       </c>
@@ -8329,7 +8495,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>161</v>
       </c>
@@ -8369,9 +8535,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EB26E8-DE87-AC44-90B8-3DA652E7A09F}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -8400,7 +8566,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>44.65</v>
       </c>
@@ -8429,7 +8595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>44.65</v>
       </c>
@@ -8458,7 +8624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>44.65</v>
       </c>
@@ -8487,7 +8653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>44.65</v>
       </c>
@@ -8516,7 +8682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>44.65</v>
       </c>
@@ -8545,7 +8711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>44.65</v>
       </c>
@@ -8574,7 +8740,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>44.65</v>
       </c>
@@ -8603,7 +8769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>44.65</v>
       </c>
@@ -8632,7 +8798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>44.65</v>
       </c>
@@ -8661,7 +8827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>44.65</v>
       </c>
@@ -8690,7 +8856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>44.65</v>
       </c>
@@ -8719,7 +8885,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>44.65</v>
       </c>
@@ -8748,7 +8914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>44.65</v>
       </c>
@@ -8785,9 +8951,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A8E028-572B-3246-AD12-59776EC25C9A}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -8816,7 +8982,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>44.65</v>
       </c>
@@ -8845,7 +9011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>44.65</v>
       </c>
@@ -8874,7 +9040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>44.65</v>
       </c>
@@ -8903,7 +9069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>44.65</v>
       </c>
@@ -8932,7 +9098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>44.65</v>
       </c>
@@ -8961,7 +9127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>44.65</v>
       </c>
@@ -8990,7 +9156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>44.65</v>
       </c>
@@ -9019,7 +9185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>44.65</v>
       </c>
@@ -9048,7 +9214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>44.65</v>
       </c>
@@ -9077,7 +9243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>44.65</v>
       </c>
@@ -9106,7 +9272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>44.65</v>
       </c>
@@ -9135,7 +9301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>44.65</v>
       </c>
@@ -9164,7 +9330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>44.65</v>
       </c>
@@ -9193,7 +9359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>44.65</v>
       </c>
@@ -9222,7 +9388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>44.65</v>
       </c>
@@ -9251,7 +9417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>44.65</v>
       </c>
@@ -9280,7 +9446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>44.65</v>
       </c>
@@ -9309,7 +9475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>44.65</v>
       </c>
@@ -9346,9 +9512,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6F9DFA-52BC-1B42-8DE6-D46F5D3105DE}">
   <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -9386,7 +9552,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>26.5</v>
       </c>
@@ -9426,7 +9592,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>26.5</v>
       </c>
@@ -9459,7 +9625,7 @@
         <v>3.5384552845528461</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>26.5</v>
       </c>
@@ -9488,7 +9654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>26.5</v>
       </c>
@@ -9525,7 +9691,7 @@
         <v>28.07739837398374</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>26.5</v>
       </c>
@@ -9558,7 +9724,7 @@
         <v>25.066016260162602</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>26.5</v>
       </c>
@@ -9587,7 +9753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>26.5</v>
       </c>
@@ -9616,7 +9782,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>26.5</v>
       </c>
@@ -9653,7 +9819,7 @@
         <v>36.513902439024399</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>26.5</v>
       </c>
@@ -9686,7 +9852,7 @@
         <v>36.630975609756106</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>26.5</v>
       </c>
@@ -9715,7 +9881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>26.5</v>
       </c>
@@ -9744,7 +9910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>26.5</v>
       </c>
@@ -9773,7 +9939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>26.5</v>
       </c>
@@ -9810,9 +9976,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782B3C6A-0DB6-E84A-83DE-01D1F8DAAE53}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -9841,7 +10007,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>-30.675000000000001</v>
       </c>
@@ -9870,7 +10036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>-30.675000000000001</v>
       </c>
@@ -9899,7 +10065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>-30.675000000000001</v>
       </c>
@@ -9928,7 +10094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>-30.675000000000001</v>
       </c>
@@ -9957,7 +10123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>-30.675000000000001</v>
       </c>
@@ -9986,7 +10152,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>-30.675000000000001</v>
       </c>
@@ -10015,7 +10181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>-30.675000000000001</v>
       </c>
@@ -10044,7 +10210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>-30.675000000000001</v>
       </c>
@@ -10073,7 +10239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>-30.675000000000001</v>
       </c>
@@ -10102,7 +10268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>-30.675000000000001</v>
       </c>
@@ -10131,7 +10297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>-30.675000000000001</v>
       </c>
@@ -10160,7 +10326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>-30.675000000000001</v>
       </c>
@@ -10189,7 +10355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>-30.675000000000001</v>
       </c>
@@ -10218,7 +10384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>-30.675000000000001</v>
       </c>
@@ -10247,7 +10413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>-30.675000000000001</v>
       </c>
@@ -10276,7 +10442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>-30.675000000000001</v>
       </c>
@@ -10305,7 +10471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>-30.675000000000001</v>
       </c>
@@ -10334,7 +10500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>-30.675000000000001</v>
       </c>
@@ -10363,7 +10529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>-30.675000000000001</v>
       </c>
@@ -10392,7 +10558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>-30.675000000000001</v>
       </c>
@@ -10421,7 +10587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>-30.675000000000001</v>
       </c>
@@ -10450,7 +10616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>-30.675000000000001</v>
       </c>
@@ -10479,7 +10645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>-30.675000000000001</v>
       </c>
@@ -10508,7 +10674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>-30.675000000000001</v>
       </c>
@@ -10537,7 +10703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>-30.675000000000001</v>
       </c>
@@ -10566,7 +10732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>-30.675000000000001</v>
       </c>
@@ -10595,7 +10761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>-30.675000000000001</v>
       </c>
@@ -10624,7 +10790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>-30.675000000000001</v>
       </c>
@@ -10653,7 +10819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>-30.675000000000001</v>
       </c>
@@ -10682,7 +10848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>-30.675000000000001</v>
       </c>
@@ -10711,7 +10877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>-30.675000000000001</v>
       </c>
@@ -10748,9 +10914,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0813EFF2-17DD-5D41-9CC5-7C5C952467AD}">
   <dimension ref="A1:R10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="D1" t="s">
         <v>169</v>
       </c>
@@ -10764,7 +10930,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -10818,7 +10984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -10871,7 +11037,7 @@
         <v>151.1833007387159</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -10924,7 +11090,7 @@
         <v>61.964911721823398</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -10975,7 +11141,7 @@
         <v>7.7399999999999997E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -11036,7 +11202,7 @@
         <v>2.4398211267921601</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -11093,7 +11259,7 @@
         <v>800.58025480391996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>183</v>
       </c>
